--- a/プロジェクト型演習_成果物_TasBo_登録.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_登録.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DACC18-F8A7-42C9-A5EB-687382A8E5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF81281-75CE-49AC-ABF5-F31EA82F40DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
-    <sheet name="ユースケース記述②" sheetId="8" r:id="rId2"/>
+    <sheet name="ユースケース記述" sheetId="8" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書（登録画面）" sheetId="5" r:id="rId5"/>
@@ -298,116 +298,9 @@
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>社員</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
     <t>タスク登録</t>
     <rPh sb="3" eb="5">
       <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>社員が新しいタスクを登録する。</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>アタラ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>利用者がシステムにログインしている。/タスク登録画面が表示されている。</t>
-    <rPh sb="0" eb="3">
-      <t>リヨウシャ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>タスク情報が登録されている。/タスク一覧に登録したタスクが表示されている。</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>1,社員はタスク登録画面を表示する。
-2,社員はタスク名を入力する。
-3,社員はカテゴリ情報を入力する。
-4,社員は期限を入力する。
-5,社員は担当者を選択する。
-6,社員はステータス情報を入力する。
-7,社員は「登録」ボタンを押下する。
-8,システムは入力内容をチェックする。
-9,システムはタスク情報を登録する。
-10.システムは登録完了メッセージを表示する。
-11,システムはタスク一覧画面へ遷移する。</t>
-    <rPh sb="2" eb="4">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="69" eb="71">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="92" eb="94">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="103" eb="105">
-      <t>シャイン</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・登録処理中にシステムエラーが発生した場合
-a,システムエラーが発生する。
-b,システムはエラーメッセージを表示する。
-c,システムは処理を終了する。
-</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>・必須項目が未入力の場合
-a,システムは入力チェックを行う。
-b,システムは未入力項目のエラーメッセージを表示する。
-c,システムはタスク登録画面を再表示する。
-d,社員は入力内容を修正する。
-・期限日が不正な場合
-a,システムは期限日の妥当性をチェックする。
-b,システムはエラーメッセージを表示する。
-c, システムはタスク登録画面を再表示する。</t>
-    <rPh sb="83" eb="85">
-      <t>シャイン</t>
     </rPh>
     <phoneticPr fontId="9"/>
   </si>
@@ -630,6 +523,58 @@
     <t>href</t>
     <phoneticPr fontId="9"/>
   </si>
+  <si>
+    <t>ユーザ</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>ユーザが新しいタスクを登録する。</t>
+    <rPh sb="4" eb="5">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>ユーザがシステムにログインしていること</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>1.ユーザはタスク名を入力する。
+2.ユーザはカテゴリを選択する。
+3.ユーザは期限日を入力する。
+4.ユーザは担当者を選択する。
+5.ユーザはステータスを選択する。
+6.ユーザは登録ボタンを押下する。
+7.システムは入力内容をチェックする。
+8.システムはタスク情報を登録する。
+9.システムは「登録が完了しました」を表示する。
+10.システムはタスク一覧画面を表示する。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>A1. 必須項目が未入力の場合（基本フロー7から分岐）
+a. システムは未入力項目を検出する。
+b. システムは該当項目のエラーメッセージ「このフィールドに入力してください。」を表示する。</t>
+    <rPh sb="78" eb="80">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>成功時 : タスク情報が登録されている。/タスク一覧画面が表示されている。/登録したタスクが一覧に表示されている。
+失敗時 : タスク情報は登録されていない。/タスク登録画面が表示されている。</t>
+    <rPh sb="0" eb="3">
+      <t>セイコウジ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
 </sst>
 </file>
 
@@ -664,6 +609,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1402,7 +1348,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1568,75 +1514,99 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1646,30 +1616,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1688,6 +1634,24 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1700,9 +1664,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1721,45 +1682,102 @@
     <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1775,83 +1793,20 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1859,29 +1814,59 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2938,67 +2923,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3021,14 +3006,14 @@
       <c r="E8" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -3038,26 +3023,26 @@
       <c r="G13" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="59"/>
+      <c r="H13" s="75"/>
       <c r="I13" s="94">
         <v>46175</v>
       </c>
-      <c r="J13" s="56"/>
-      <c r="K13" s="59"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="75"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="89"/>
-      <c r="H14" s="59"/>
+      <c r="H14" s="75"/>
       <c r="I14" s="89"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="59"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="75"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="89"/>
-      <c r="H15" s="59"/>
+      <c r="H15" s="75"/>
       <c r="I15" s="89"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="59"/>
+      <c r="J15" s="74"/>
+      <c r="K15" s="75"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3069,10 +3054,10 @@
       <c r="G17" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4086,182 +4071,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="63" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="63" t="s">
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="63" t="s">
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="63" t="s">
+      <c r="P1" s="71"/>
+      <c r="Q1" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="62"/>
-      <c r="S1" s="63" t="s">
+      <c r="R1" s="71"/>
+      <c r="S1" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="66"/>
+      <c r="T1" s="78"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="75"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="69"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="82"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="72"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="83"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="104"/>
-      <c r="P4" s="103"/>
-      <c r="Q4" s="104"/>
-      <c r="R4" s="103"/>
-      <c r="S4" s="104"/>
-      <c r="T4" s="158"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="107"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="109"/>
+      <c r="P4" s="108"/>
+      <c r="Q4" s="109"/>
+      <c r="R4" s="108"/>
+      <c r="S4" s="109"/>
+      <c r="T4" s="152"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="98" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="66"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="70"/>
+      <c r="Q5" s="70"/>
+      <c r="R5" s="70"/>
+      <c r="S5" s="70"/>
+      <c r="T5" s="78"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="55" t="s">
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="56"/>
-      <c r="R6" s="56"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="57"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="74"/>
+      <c r="P6" s="74"/>
+      <c r="Q6" s="74"/>
+      <c r="R6" s="74"/>
+      <c r="S6" s="74"/>
+      <c r="T6" s="79"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="55" t="s">
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="56"/>
-      <c r="T7" s="57"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="74"/>
+      <c r="O7" s="74"/>
+      <c r="P7" s="74"/>
+      <c r="Q7" s="74"/>
+      <c r="R7" s="74"/>
+      <c r="S7" s="74"/>
+      <c r="T7" s="79"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -4460,37 +4445,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="64" t="s">
+      <c r="A15" s="76" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="157" t="s">
+      <c r="B15" s="75"/>
+      <c r="C15" s="155" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="59"/>
-      <c r="E15" s="73" t="s">
+      <c r="D15" s="75"/>
+      <c r="E15" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="73" t="s">
+      <c r="F15" s="75"/>
+      <c r="G15" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="56"/>
-      <c r="I15" s="59"/>
-      <c r="J15" s="73" t="s">
+      <c r="H15" s="74"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="59"/>
-      <c r="L15" s="73" t="s">
+      <c r="K15" s="75"/>
+      <c r="L15" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="56"/>
-      <c r="N15" s="59"/>
-      <c r="O15" s="73" t="s">
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="56"/>
-      <c r="Q15" s="59"/>
+      <c r="P15" s="74"/>
+      <c r="Q15" s="75"/>
       <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
@@ -4502,37 +4487,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="150">
+      <c r="A16" s="153">
         <v>1</v>
       </c>
-      <c r="B16" s="59"/>
-      <c r="C16" s="151" t="s">
+      <c r="B16" s="75"/>
+      <c r="C16" s="154" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="59"/>
-      <c r="E16" s="151" t="s">
+      <c r="D16" s="75"/>
+      <c r="E16" s="154" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="59"/>
-      <c r="G16" s="156" t="s">
+      <c r="F16" s="75"/>
+      <c r="G16" s="148" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="56"/>
-      <c r="I16" s="59"/>
-      <c r="J16" s="156" t="s">
+      <c r="H16" s="74"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="148" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="59"/>
-      <c r="L16" s="154" t="s">
+      <c r="K16" s="75"/>
+      <c r="L16" s="150" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="56"/>
-      <c r="N16" s="59"/>
-      <c r="O16" s="154" t="s">
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="150" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="56"/>
-      <c r="Q16" s="59"/>
+      <c r="P16" s="74"/>
+      <c r="Q16" s="75"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -4544,37 +4529,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="150">
+      <c r="A17" s="153">
         <v>2</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="151" t="s">
+      <c r="B17" s="75"/>
+      <c r="C17" s="154" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="59"/>
-      <c r="E17" s="151" t="s">
+      <c r="D17" s="75"/>
+      <c r="E17" s="154" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="59"/>
-      <c r="G17" s="156" t="s">
+      <c r="F17" s="75"/>
+      <c r="G17" s="148" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="56"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="156" t="s">
+      <c r="H17" s="74"/>
+      <c r="I17" s="75"/>
+      <c r="J17" s="148" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="59"/>
-      <c r="L17" s="154" t="s">
+      <c r="K17" s="75"/>
+      <c r="L17" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="56"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="154" t="s">
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="150" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="56"/>
-      <c r="Q17" s="59"/>
+      <c r="P17" s="74"/>
+      <c r="Q17" s="75"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -4586,23 +4571,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="150"/>
-      <c r="B18" s="59"/>
-      <c r="C18" s="151"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="151"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="156"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="59"/>
-      <c r="J18" s="156"/>
-      <c r="K18" s="59"/>
-      <c r="L18" s="154"/>
-      <c r="M18" s="56"/>
-      <c r="N18" s="59"/>
-      <c r="O18" s="154"/>
-      <c r="P18" s="56"/>
-      <c r="Q18" s="59"/>
+      <c r="A18" s="153"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="154"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="154"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="148"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="75"/>
+      <c r="L18" s="150"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="150"/>
+      <c r="P18" s="74"/>
+      <c r="Q18" s="75"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -4614,23 +4599,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="150"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="151"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="151"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="156"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="156"/>
-      <c r="K19" s="59"/>
-      <c r="L19" s="154"/>
-      <c r="M19" s="56"/>
-      <c r="N19" s="59"/>
-      <c r="O19" s="154"/>
-      <c r="P19" s="56"/>
-      <c r="Q19" s="59"/>
+      <c r="A19" s="153"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="154"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="154"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="148"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="75"/>
+      <c r="J19" s="148"/>
+      <c r="K19" s="75"/>
+      <c r="L19" s="150"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="150"/>
+      <c r="P19" s="74"/>
+      <c r="Q19" s="75"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -4642,23 +4627,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="150"/>
-      <c r="B20" s="59"/>
-      <c r="C20" s="151"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="151"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="156"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="59"/>
-      <c r="J20" s="156"/>
-      <c r="K20" s="59"/>
-      <c r="L20" s="154"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="154"/>
-      <c r="P20" s="56"/>
-      <c r="Q20" s="59"/>
+      <c r="A20" s="153"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="154"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="154"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="148"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="75"/>
+      <c r="J20" s="148"/>
+      <c r="K20" s="75"/>
+      <c r="L20" s="150"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="150"/>
+      <c r="P20" s="74"/>
+      <c r="Q20" s="75"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -4670,23 +4655,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="150"/>
-      <c r="B21" s="59"/>
-      <c r="C21" s="151"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="151"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="156"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="156"/>
-      <c r="K21" s="59"/>
-      <c r="L21" s="154"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="154"/>
-      <c r="P21" s="56"/>
-      <c r="Q21" s="59"/>
+      <c r="A21" s="153"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="154"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="154"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="148"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="75"/>
+      <c r="J21" s="148"/>
+      <c r="K21" s="75"/>
+      <c r="L21" s="150"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="150"/>
+      <c r="P21" s="74"/>
+      <c r="Q21" s="75"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -4698,23 +4683,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="150"/>
-      <c r="B22" s="59"/>
-      <c r="C22" s="151"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="151"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="156"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="156"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="154"/>
-      <c r="M22" s="56"/>
-      <c r="N22" s="59"/>
-      <c r="O22" s="154"/>
-      <c r="P22" s="56"/>
-      <c r="Q22" s="59"/>
+      <c r="A22" s="153"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="154"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="154"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="148"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="75"/>
+      <c r="J22" s="148"/>
+      <c r="K22" s="75"/>
+      <c r="L22" s="150"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="150"/>
+      <c r="P22" s="74"/>
+      <c r="Q22" s="75"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -4726,23 +4711,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="150"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="151"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="151"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="156"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="156"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="154"/>
-      <c r="M23" s="56"/>
-      <c r="N23" s="59"/>
-      <c r="O23" s="154"/>
-      <c r="P23" s="56"/>
-      <c r="Q23" s="59"/>
+      <c r="A23" s="153"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="154"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="154"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="148"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="75"/>
+      <c r="J23" s="148"/>
+      <c r="K23" s="75"/>
+      <c r="L23" s="150"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="150"/>
+      <c r="P23" s="74"/>
+      <c r="Q23" s="75"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -4754,23 +4739,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="150"/>
-      <c r="B24" s="59"/>
-      <c r="C24" s="151"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="156"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="156"/>
-      <c r="K24" s="59"/>
-      <c r="L24" s="154"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="59"/>
-      <c r="O24" s="154"/>
-      <c r="P24" s="56"/>
-      <c r="Q24" s="59"/>
+      <c r="A24" s="153"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="154"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="148"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="148"/>
+      <c r="K24" s="75"/>
+      <c r="L24" s="150"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="150"/>
+      <c r="P24" s="74"/>
+      <c r="Q24" s="75"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -4782,23 +4767,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="150"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="151"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="151"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="156"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="156"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="154"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="59"/>
-      <c r="O25" s="154"/>
-      <c r="P25" s="56"/>
-      <c r="Q25" s="59"/>
+      <c r="A25" s="153"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="154"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="148"/>
+      <c r="H25" s="74"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="148"/>
+      <c r="K25" s="75"/>
+      <c r="L25" s="150"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="150"/>
+      <c r="P25" s="74"/>
+      <c r="Q25" s="75"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -4810,23 +4795,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="150"/>
-      <c r="B26" s="59"/>
-      <c r="C26" s="151"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="151"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="156"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="156"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="154"/>
-      <c r="M26" s="56"/>
-      <c r="N26" s="59"/>
-      <c r="O26" s="154"/>
-      <c r="P26" s="56"/>
-      <c r="Q26" s="59"/>
+      <c r="A26" s="153"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="154"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="148"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="148"/>
+      <c r="K26" s="75"/>
+      <c r="L26" s="150"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="150"/>
+      <c r="P26" s="74"/>
+      <c r="Q26" s="75"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -4838,23 +4823,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="150"/>
-      <c r="B27" s="59"/>
-      <c r="C27" s="151"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="156"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="156"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="154"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="59"/>
-      <c r="O27" s="154"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="59"/>
+      <c r="A27" s="153"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="154"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="154"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="148"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="148"/>
+      <c r="K27" s="75"/>
+      <c r="L27" s="150"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="150"/>
+      <c r="P27" s="74"/>
+      <c r="Q27" s="75"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -4866,23 +4851,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="150"/>
-      <c r="B28" s="59"/>
-      <c r="C28" s="151"/>
-      <c r="D28" s="59"/>
-      <c r="E28" s="151"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="156"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="156"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="154"/>
-      <c r="M28" s="56"/>
-      <c r="N28" s="59"/>
-      <c r="O28" s="154"/>
-      <c r="P28" s="56"/>
-      <c r="Q28" s="59"/>
+      <c r="A28" s="153"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="154"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="154"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="148"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="75"/>
+      <c r="J28" s="148"/>
+      <c r="K28" s="75"/>
+      <c r="L28" s="150"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="150"/>
+      <c r="P28" s="74"/>
+      <c r="Q28" s="75"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -4894,23 +4879,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="150"/>
-      <c r="B29" s="59"/>
-      <c r="C29" s="151"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="151"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="156"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="59"/>
-      <c r="J29" s="156"/>
-      <c r="K29" s="59"/>
-      <c r="L29" s="154"/>
-      <c r="M29" s="56"/>
-      <c r="N29" s="59"/>
-      <c r="O29" s="154"/>
-      <c r="P29" s="56"/>
-      <c r="Q29" s="59"/>
+      <c r="A29" s="153"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="154"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="154"/>
+      <c r="F29" s="75"/>
+      <c r="G29" s="148"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="75"/>
+      <c r="J29" s="148"/>
+      <c r="K29" s="75"/>
+      <c r="L29" s="150"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="150"/>
+      <c r="P29" s="74"/>
+      <c r="Q29" s="75"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -4922,23 +4907,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="150"/>
-      <c r="B30" s="59"/>
-      <c r="C30" s="151"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="151"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="156"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="59"/>
-      <c r="J30" s="156"/>
-      <c r="K30" s="59"/>
-      <c r="L30" s="154"/>
-      <c r="M30" s="56"/>
-      <c r="N30" s="59"/>
-      <c r="O30" s="154"/>
-      <c r="P30" s="56"/>
-      <c r="Q30" s="59"/>
+      <c r="A30" s="153"/>
+      <c r="B30" s="75"/>
+      <c r="C30" s="154"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="154"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="148"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="75"/>
+      <c r="J30" s="148"/>
+      <c r="K30" s="75"/>
+      <c r="L30" s="150"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="150"/>
+      <c r="P30" s="74"/>
+      <c r="Q30" s="75"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -4950,23 +4935,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="152"/>
-      <c r="B31" s="107"/>
-      <c r="C31" s="153"/>
-      <c r="D31" s="107"/>
-      <c r="E31" s="153"/>
-      <c r="F31" s="107"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="79"/>
-      <c r="I31" s="107"/>
-      <c r="J31" s="159"/>
-      <c r="K31" s="107"/>
-      <c r="L31" s="155"/>
-      <c r="M31" s="79"/>
-      <c r="N31" s="107"/>
-      <c r="O31" s="155"/>
-      <c r="P31" s="79"/>
-      <c r="Q31" s="107"/>
+      <c r="A31" s="156"/>
+      <c r="B31" s="97"/>
+      <c r="C31" s="157"/>
+      <c r="D31" s="97"/>
+      <c r="E31" s="157"/>
+      <c r="F31" s="97"/>
+      <c r="G31" s="149"/>
+      <c r="H31" s="87"/>
+      <c r="I31" s="97"/>
+      <c r="J31" s="149"/>
+      <c r="K31" s="97"/>
+      <c r="L31" s="151"/>
+      <c r="M31" s="87"/>
+      <c r="N31" s="97"/>
+      <c r="O31" s="151"/>
+      <c r="P31" s="87"/>
+      <c r="Q31" s="97"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -5964,62 +5949,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -6044,62 +6029,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -6118,19 +6103,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="63" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="63" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="62"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -6142,192 +6127,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="105">
+      <c r="G2" s="56"/>
+      <c r="H2" s="110">
         <v>46175</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="62"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="96"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="98" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="66"/>
+      <c r="B5" s="171"/>
+      <c r="C5" s="172"/>
+      <c r="D5" s="104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="170"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="57"/>
+      <c r="B6" s="163"/>
+      <c r="C6" s="160"/>
+      <c r="D6" s="84" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="164"/>
+      <c r="F6" s="164"/>
+      <c r="G6" s="164"/>
+      <c r="H6" s="164"/>
+      <c r="I6" s="164"/>
+      <c r="J6" s="165"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="99" t="s">
+      <c r="A7" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="57"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="84" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="164"/>
+      <c r="H7" s="164"/>
+      <c r="I7" s="164"/>
+      <c r="J7" s="165"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="99" t="s">
+      <c r="A8" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="108" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="57"/>
+      <c r="B8" s="163"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="98" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="158"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="158"/>
+      <c r="I8" s="158"/>
+      <c r="J8" s="159"/>
     </row>
     <row r="9" spans="1:10" ht="159.75" customHeight="1">
-      <c r="A9" s="109" t="s">
+      <c r="A9" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="112" t="s">
+      <c r="B9" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="59"/>
-      <c r="D9" s="108" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="57"/>
-    </row>
-    <row r="10" spans="1:10" ht="133.5" customHeight="1">
-      <c r="A10" s="110"/>
-      <c r="B10" s="112" t="s">
+      <c r="C9" s="160"/>
+      <c r="D9" s="98" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="158"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="158"/>
+      <c r="H9" s="158"/>
+      <c r="I9" s="158"/>
+      <c r="J9" s="159"/>
+    </row>
+    <row r="10" spans="1:10" ht="83.25" customHeight="1">
+      <c r="A10" s="161"/>
+      <c r="B10" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="59"/>
-      <c r="D10" s="108" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="57"/>
+      <c r="C10" s="160"/>
+      <c r="D10" s="98" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="158"/>
+      <c r="F10" s="158"/>
+      <c r="G10" s="158"/>
+      <c r="H10" s="158"/>
+      <c r="I10" s="158"/>
+      <c r="J10" s="159"/>
     </row>
     <row r="11" spans="1:10" ht="68.25" customHeight="1">
-      <c r="A11" s="111"/>
-      <c r="B11" s="112" t="s">
+      <c r="A11" s="162"/>
+      <c r="B11" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="59"/>
-      <c r="D11" s="108" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="57"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="99" t="s">
+      <c r="C11" s="160"/>
+      <c r="D11" s="98" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="158"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="158"/>
+      <c r="H11" s="158"/>
+      <c r="I11" s="158"/>
+      <c r="J11" s="159"/>
+    </row>
+    <row r="12" spans="1:10" ht="66.75" customHeight="1">
+      <c r="A12" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="55" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="57"/>
+      <c r="B12" s="163"/>
+      <c r="C12" s="160"/>
+      <c r="D12" s="98" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="164"/>
+      <c r="F12" s="164"/>
+      <c r="G12" s="164"/>
+      <c r="H12" s="164"/>
+      <c r="I12" s="164"/>
+      <c r="J12" s="165"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="106" t="s">
+      <c r="A13" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="79"/>
-      <c r="C13" s="107"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="80"/>
+      <c r="B13" s="168"/>
+      <c r="C13" s="169"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="166"/>
+      <c r="G13" s="166"/>
+      <c r="H13" s="166"/>
+      <c r="I13" s="166"/>
+      <c r="J13" s="167"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7318,6 +7303,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -7333,18 +7330,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7363,19 +7348,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="63" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="63" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="62"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7387,40 +7372,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="84"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="96"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8776,19 +8761,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="63" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="63" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="62"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -8800,48 +8785,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="113">
+      <c r="G2" s="56"/>
+      <c r="H2" s="111">
         <v>46175</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="62"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="96"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10192,19 +10177,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="63" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="63" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="62"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -10216,203 +10201,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="81">
+      <c r="G2" s="56"/>
+      <c r="H2" s="59">
         <v>46175</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="62"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="65" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="66"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="77" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="78"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="57"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="79"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="67"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="69"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="82"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="70"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="72"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="83"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="70"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="72"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="83"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="70"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="72"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="83"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="72"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="83"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="70"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="72"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="83"/>
     </row>
     <row r="13" spans="1:10" ht="93" customHeight="1">
-      <c r="A13" s="70"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="72"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="83"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="57"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="79"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="64" t="s">
+      <c r="A15" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="59"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="84" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="75"/>
       <c r="I15" s="15" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="59"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="75"/>
       <c r="D16" s="15" t="s">
         <v>27</v>
       </c>
@@ -10425,155 +10410,155 @@
       <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="73" t="s">
+      <c r="H16" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="56"/>
-      <c r="J16" s="57"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="79"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="58">
+      <c r="A17" s="73">
         <v>1</v>
       </c>
-      <c r="B17" s="56"/>
-      <c r="C17" s="59"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="75"/>
       <c r="D17" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="84"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="79"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="73">
+        <v>2</v>
+      </c>
+      <c r="B18" s="74"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="84"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="79"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="73">
+        <v>3</v>
+      </c>
+      <c r="B19" s="74"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="84"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="79"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="73">
+        <v>4</v>
+      </c>
+      <c r="B20" s="74"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="84"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="79"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="73">
+        <v>5</v>
+      </c>
+      <c r="B21" s="74"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="84"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="79"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="73">
+        <v>6</v>
+      </c>
+      <c r="B22" s="74"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H17" s="55"/>
-      <c r="I17" s="56"/>
-      <c r="J17" s="57"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="58">
-        <v>2</v>
-      </c>
-      <c r="B18" s="56"/>
-      <c r="C18" s="59"/>
-      <c r="D18" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="H18" s="55"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="57"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="58">
-        <v>3</v>
-      </c>
-      <c r="B19" s="56"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="17" t="s">
+      <c r="E22" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H19" s="55"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="57"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="58">
-        <v>4</v>
-      </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H20" s="55"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="57"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="58">
-        <v>5</v>
-      </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="55"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="57"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="58">
-        <v>6</v>
-      </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>92</v>
-      </c>
       <c r="G22" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H22" s="55"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="57"/>
+        <v>76</v>
+      </c>
+      <c r="H22" s="84"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="79"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="58"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="59"/>
+      <c r="A23" s="73"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="75"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="80"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="87"/>
+      <c r="J23" s="88"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11554,11 +11539,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -11575,16 +11565,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11607,19 +11592,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="63" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="63" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="62"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -11631,203 +11616,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="81">
+      <c r="G2" s="56"/>
+      <c r="H2" s="59">
         <v>46175</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="62"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="65" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="66"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="78"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="57"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="79"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="67"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="69"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="82"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="70"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="72"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="83"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="70"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="72"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="83"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="70"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="72"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="83"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="72"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="83"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="70"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="72"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="83"/>
     </row>
     <row r="13" spans="1:10" ht="93" customHeight="1">
-      <c r="A13" s="70"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="72"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="83"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="57"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="79"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="64" t="s">
+      <c r="A15" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="59"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="84" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="75"/>
       <c r="I15" s="15" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="59"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="75"/>
       <c r="D16" s="15" t="s">
         <v>27</v>
       </c>
@@ -11840,103 +11825,103 @@
       <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="73" t="s">
+      <c r="H16" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="56"/>
-      <c r="J16" s="57"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="79"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="58">
+      <c r="A17" s="73">
         <v>1</v>
       </c>
-      <c r="B17" s="56"/>
-      <c r="C17" s="59"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="75"/>
       <c r="D17" s="17" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="H17" s="55"/>
-      <c r="I17" s="56"/>
-      <c r="J17" s="57"/>
+        <v>108</v>
+      </c>
+      <c r="H17" s="84"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="79"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="58"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="59"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="75"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="57"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="79"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="58"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="59"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="75"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="57"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="79"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="58"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="59"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="75"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="57"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="79"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="58"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="59"/>
+      <c r="A21" s="73"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="75"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="57"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="79"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="58"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="59"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="75"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="57"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="79"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="58"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="59"/>
+      <c r="A23" s="73"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="75"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="80"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="87"/>
+      <c r="J23" s="88"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12917,22 +12902,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -12948,6 +12917,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12970,19 +12955,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="63" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="63" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="62"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -12994,203 +12979,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="81">
+      <c r="G2" s="56"/>
+      <c r="H2" s="59">
         <v>46175</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="62"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="65" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="66"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="77" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="78"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="57"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="79"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="67"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="69"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="82"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="70"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="72"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="83"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="70"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="72"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="83"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="70"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="72"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="83"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="72"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="83"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="70"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="72"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="83"/>
     </row>
     <row r="13" spans="1:10" ht="93" customHeight="1">
-      <c r="A13" s="70"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="72"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="83"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="57"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="79"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="64" t="s">
+      <c r="A15" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="59"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="84" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="75"/>
       <c r="I15" s="15" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="59"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="75"/>
       <c r="D16" s="15" t="s">
         <v>27</v>
       </c>
@@ -13203,103 +13188,103 @@
       <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="73" t="s">
+      <c r="H16" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="56"/>
-      <c r="J16" s="57"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="79"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="58">
+      <c r="A17" s="73">
         <v>1</v>
       </c>
-      <c r="B17" s="56"/>
-      <c r="C17" s="59"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="75"/>
       <c r="D17" s="17" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="H17" s="55"/>
-      <c r="I17" s="56"/>
-      <c r="J17" s="57"/>
+        <v>110</v>
+      </c>
+      <c r="H17" s="84"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="79"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="58"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="59"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="75"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="57"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="79"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="58"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="59"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="75"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="57"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="79"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="58"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="59"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="75"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="57"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="79"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="58"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="59"/>
+      <c r="A21" s="73"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="75"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="57"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="79"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="58"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="59"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="75"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="57"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="79"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="58"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="59"/>
+      <c r="A23" s="73"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="75"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="80"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="87"/>
+      <c r="J23" s="88"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14280,22 +14265,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -14311,6 +14280,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14332,19 +14317,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="149" t="s">
+      <c r="B1" s="137"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="149" t="s">
+      <c r="E1" s="127"/>
+      <c r="F1" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="127"/>
       <c r="H1" s="52" t="s">
         <v>5</v>
       </c>
@@ -14356,205 +14341,205 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="143"/>
-      <c r="B2" s="144"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="126" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="127"/>
-      <c r="F2" s="126" t="s">
-        <v>103</v>
-      </c>
-      <c r="G2" s="127"/>
-      <c r="H2" s="130">
+      <c r="A2" s="133"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="112" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="113"/>
+      <c r="F2" s="112" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="113"/>
+      <c r="H2" s="116">
         <v>46176</v>
       </c>
-      <c r="I2" s="132" t="s">
-        <v>102</v>
-      </c>
-      <c r="J2" s="133"/>
+      <c r="I2" s="122" t="s">
+        <v>95</v>
+      </c>
+      <c r="J2" s="123"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="143"/>
-      <c r="B3" s="144"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="128"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="134"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="124"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A4" s="143"/>
-      <c r="B4" s="144"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="134"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="124"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="135" t="s">
+      <c r="A5" s="125" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="136"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="138" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="139"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="128" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="129"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="124" t="s">
+      <c r="A6" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="115"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="118"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="120"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="140" t="e" vm="1">
+      <c r="A7" s="130" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="141"/>
-      <c r="C7" s="141"/>
-      <c r="D7" s="141"/>
-      <c r="E7" s="141"/>
-      <c r="F7" s="141"/>
-      <c r="G7" s="141"/>
-      <c r="H7" s="141"/>
-      <c r="I7" s="141"/>
-      <c r="J7" s="142"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="131"/>
+      <c r="J7" s="132"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="143"/>
-      <c r="B8" s="144"/>
-      <c r="C8" s="144"/>
-      <c r="D8" s="144"/>
-      <c r="E8" s="144"/>
-      <c r="F8" s="144"/>
-      <c r="G8" s="144"/>
-      <c r="H8" s="144"/>
-      <c r="I8" s="144"/>
-      <c r="J8" s="145"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="134"/>
+      <c r="D8" s="134"/>
+      <c r="E8" s="134"/>
+      <c r="F8" s="134"/>
+      <c r="G8" s="134"/>
+      <c r="H8" s="134"/>
+      <c r="I8" s="134"/>
+      <c r="J8" s="135"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="143"/>
-      <c r="B9" s="144"/>
-      <c r="C9" s="144"/>
-      <c r="D9" s="144"/>
-      <c r="E9" s="144"/>
-      <c r="F9" s="144"/>
-      <c r="G9" s="144"/>
-      <c r="H9" s="144"/>
-      <c r="I9" s="144"/>
-      <c r="J9" s="145"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="134"/>
+      <c r="C9" s="134"/>
+      <c r="D9" s="134"/>
+      <c r="E9" s="134"/>
+      <c r="F9" s="134"/>
+      <c r="G9" s="134"/>
+      <c r="H9" s="134"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="135"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="143"/>
-      <c r="B10" s="144"/>
-      <c r="C10" s="144"/>
-      <c r="D10" s="144"/>
-      <c r="E10" s="144"/>
-      <c r="F10" s="144"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="144"/>
-      <c r="J10" s="145"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="134"/>
+      <c r="C10" s="134"/>
+      <c r="D10" s="134"/>
+      <c r="E10" s="134"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="135"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="143"/>
-      <c r="B11" s="144"/>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="145"/>
+      <c r="A11" s="133"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="134"/>
+      <c r="E11" s="134"/>
+      <c r="F11" s="134"/>
+      <c r="G11" s="134"/>
+      <c r="H11" s="134"/>
+      <c r="I11" s="134"/>
+      <c r="J11" s="135"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="143"/>
-      <c r="B12" s="144"/>
-      <c r="C12" s="144"/>
-      <c r="D12" s="144"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="144"/>
-      <c r="J12" s="145"/>
+      <c r="A12" s="133"/>
+      <c r="B12" s="134"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="134"/>
+      <c r="F12" s="134"/>
+      <c r="G12" s="134"/>
+      <c r="H12" s="134"/>
+      <c r="I12" s="134"/>
+      <c r="J12" s="135"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="143"/>
-      <c r="B13" s="144"/>
-      <c r="C13" s="144"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="145"/>
+      <c r="A13" s="133"/>
+      <c r="B13" s="134"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="134"/>
+      <c r="H13" s="134"/>
+      <c r="I13" s="134"/>
+      <c r="J13" s="135"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="124" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="115"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="118"/>
+      <c r="A14" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="119"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="119"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="115"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="117" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="116"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="121"/>
+      <c r="D15" s="140" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="119"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="121"/>
       <c r="I15" s="43" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="115"/>
-      <c r="C16" s="116"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="121"/>
       <c r="D16" s="43" t="s">
         <v>27</v>
       </c>
@@ -14567,106 +14552,122 @@
       <c r="G16" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="125" t="s">
+      <c r="H16" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="115"/>
-      <c r="J16" s="118"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="114">
+      <c r="A17" s="142">
         <v>1</v>
       </c>
-      <c r="B17" s="115"/>
-      <c r="C17" s="116"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="121"/>
       <c r="D17" s="42" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E17" s="42" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F17" s="41"/>
       <c r="G17" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="H17" s="117"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="118"/>
+        <v>89</v>
+      </c>
+      <c r="H17" s="140"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="114"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
+      <c r="A18" s="142"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="121"/>
       <c r="D18" s="42"/>
       <c r="E18" s="42"/>
       <c r="F18" s="41"/>
       <c r="G18" s="41"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="118"/>
+      <c r="H18" s="140"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="114"/>
-      <c r="B19" s="115"/>
-      <c r="C19" s="116"/>
+      <c r="A19" s="142"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="121"/>
       <c r="D19" s="42"/>
       <c r="E19" s="42"/>
       <c r="F19" s="41"/>
       <c r="G19" s="41"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="118"/>
+      <c r="H19" s="140"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="120"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="114"/>
-      <c r="B20" s="115"/>
-      <c r="C20" s="116"/>
+      <c r="A20" s="142"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="121"/>
       <c r="D20" s="42"/>
       <c r="E20" s="42"/>
       <c r="F20" s="41"/>
       <c r="G20" s="41"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="118"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="120"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="114"/>
-      <c r="B21" s="115"/>
-      <c r="C21" s="116"/>
+      <c r="A21" s="142"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="121"/>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
       <c r="F21" s="41"/>
       <c r="G21" s="41"/>
-      <c r="H21" s="117"/>
-      <c r="I21" s="115"/>
-      <c r="J21" s="118"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="120"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="114"/>
-      <c r="B22" s="115"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="142"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="121"/>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
       <c r="F22" s="41"/>
       <c r="G22" s="41"/>
-      <c r="H22" s="117"/>
-      <c r="I22" s="115"/>
-      <c r="J22" s="118"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="120"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A23" s="119"/>
-      <c r="B23" s="120"/>
-      <c r="C23" s="121"/>
+      <c r="A23" s="143"/>
+      <c r="B23" s="144"/>
+      <c r="C23" s="145"/>
       <c r="D23" s="40"/>
       <c r="E23" s="40"/>
       <c r="F23" s="39"/>
       <c r="G23" s="39"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="120"/>
-      <c r="J23" s="123"/>
+      <c r="H23" s="146"/>
+      <c r="I23" s="144"/>
+      <c r="J23" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
@@ -14682,22 +14683,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14719,19 +14704,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="149" t="s">
+      <c r="B1" s="137"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="149" t="s">
+      <c r="E1" s="127"/>
+      <c r="F1" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="127"/>
       <c r="H1" s="52" t="s">
         <v>5</v>
       </c>
@@ -14743,205 +14728,205 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="143"/>
-      <c r="B2" s="144"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="126" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="127"/>
-      <c r="F2" s="126" t="s">
-        <v>103</v>
-      </c>
-      <c r="G2" s="127"/>
-      <c r="H2" s="130">
+      <c r="A2" s="133"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="112" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="113"/>
+      <c r="F2" s="112" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="113"/>
+      <c r="H2" s="116">
         <v>46176</v>
       </c>
-      <c r="I2" s="132" t="s">
-        <v>102</v>
-      </c>
-      <c r="J2" s="133"/>
+      <c r="I2" s="122" t="s">
+        <v>95</v>
+      </c>
+      <c r="J2" s="123"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="143"/>
-      <c r="B3" s="144"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="128"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="134"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="124"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A4" s="143"/>
-      <c r="B4" s="144"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="134"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="124"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="135" t="s">
+      <c r="A5" s="125" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="136"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="138" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="139"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="129"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="124" t="s">
+      <c r="A6" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="115"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="118"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="120"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="140" t="e" vm="2">
+      <c r="A7" s="130" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="141"/>
-      <c r="C7" s="141"/>
-      <c r="D7" s="141"/>
-      <c r="E7" s="141"/>
-      <c r="F7" s="141"/>
-      <c r="G7" s="141"/>
-      <c r="H7" s="141"/>
-      <c r="I7" s="141"/>
-      <c r="J7" s="142"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="131"/>
+      <c r="J7" s="132"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="143"/>
-      <c r="B8" s="144"/>
-      <c r="C8" s="144"/>
-      <c r="D8" s="144"/>
-      <c r="E8" s="144"/>
-      <c r="F8" s="144"/>
-      <c r="G8" s="144"/>
-      <c r="H8" s="144"/>
-      <c r="I8" s="144"/>
-      <c r="J8" s="145"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="134"/>
+      <c r="D8" s="134"/>
+      <c r="E8" s="134"/>
+      <c r="F8" s="134"/>
+      <c r="G8" s="134"/>
+      <c r="H8" s="134"/>
+      <c r="I8" s="134"/>
+      <c r="J8" s="135"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="143"/>
-      <c r="B9" s="144"/>
-      <c r="C9" s="144"/>
-      <c r="D9" s="144"/>
-      <c r="E9" s="144"/>
-      <c r="F9" s="144"/>
-      <c r="G9" s="144"/>
-      <c r="H9" s="144"/>
-      <c r="I9" s="144"/>
-      <c r="J9" s="145"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="134"/>
+      <c r="C9" s="134"/>
+      <c r="D9" s="134"/>
+      <c r="E9" s="134"/>
+      <c r="F9" s="134"/>
+      <c r="G9" s="134"/>
+      <c r="H9" s="134"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="135"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="143"/>
-      <c r="B10" s="144"/>
-      <c r="C10" s="144"/>
-      <c r="D10" s="144"/>
-      <c r="E10" s="144"/>
-      <c r="F10" s="144"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="144"/>
-      <c r="J10" s="145"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="134"/>
+      <c r="C10" s="134"/>
+      <c r="D10" s="134"/>
+      <c r="E10" s="134"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="135"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="143"/>
-      <c r="B11" s="144"/>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="145"/>
+      <c r="A11" s="133"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="134"/>
+      <c r="E11" s="134"/>
+      <c r="F11" s="134"/>
+      <c r="G11" s="134"/>
+      <c r="H11" s="134"/>
+      <c r="I11" s="134"/>
+      <c r="J11" s="135"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="143"/>
-      <c r="B12" s="144"/>
-      <c r="C12" s="144"/>
-      <c r="D12" s="144"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="144"/>
-      <c r="J12" s="145"/>
+      <c r="A12" s="133"/>
+      <c r="B12" s="134"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="134"/>
+      <c r="F12" s="134"/>
+      <c r="G12" s="134"/>
+      <c r="H12" s="134"/>
+      <c r="I12" s="134"/>
+      <c r="J12" s="135"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="143"/>
-      <c r="B13" s="144"/>
-      <c r="C13" s="144"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="145"/>
+      <c r="A13" s="133"/>
+      <c r="B13" s="134"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="134"/>
+      <c r="H13" s="134"/>
+      <c r="I13" s="134"/>
+      <c r="J13" s="135"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="124" t="s">
+      <c r="A14" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="115"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="118"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="119"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="124" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="115"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="117" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="116"/>
+      <c r="A15" s="118" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="119"/>
+      <c r="C15" s="121"/>
+      <c r="D15" s="140" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" s="119"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="121"/>
       <c r="I15" s="43" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="115"/>
-      <c r="C16" s="116"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="121"/>
       <c r="D16" s="43" t="s">
         <v>27</v>
       </c>
@@ -14954,70 +14939,70 @@
       <c r="G16" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="125" t="s">
+      <c r="H16" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="115"/>
-      <c r="J16" s="118"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="114">
+      <c r="A17" s="142">
         <v>1</v>
       </c>
-      <c r="B17" s="115"/>
-      <c r="C17" s="116"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="121"/>
       <c r="D17" s="42" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E17" s="42" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F17" s="41"/>
       <c r="G17" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="H17" s="117"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="118"/>
+        <v>103</v>
+      </c>
+      <c r="H17" s="140"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="114"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
+      <c r="A18" s="142"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="121"/>
       <c r="D18" s="42"/>
       <c r="E18" s="42"/>
       <c r="F18" s="41"/>
       <c r="G18" s="41"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="118"/>
+      <c r="H18" s="140"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="124" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="115"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="117" t="s">
-        <v>109</v>
-      </c>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="116"/>
+      <c r="A19" s="118" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="119"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="140" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="121"/>
       <c r="I19" s="43" t="s">
         <v>25</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="124" t="s">
+      <c r="A20" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="115"/>
-      <c r="C20" s="116"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="121"/>
       <c r="D20" s="43" t="s">
         <v>27</v>
       </c>
@@ -15030,31 +15015,31 @@
       <c r="G20" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H20" s="125" t="s">
+      <c r="H20" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="115"/>
-      <c r="J20" s="118"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="120"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="114">
+      <c r="A21" s="142">
         <v>2</v>
       </c>
-      <c r="B21" s="115"/>
-      <c r="C21" s="116"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="121"/>
       <c r="D21" s="42" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F21" s="41"/>
       <c r="G21" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="H21" s="117"/>
-      <c r="I21" s="115"/>
-      <c r="J21" s="118"/>
+        <v>100</v>
+      </c>
+      <c r="H21" s="140"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="120"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="47"/>
@@ -15069,31 +15054,31 @@
       <c r="J22" s="45"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="124" t="s">
-        <v>106</v>
-      </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="116"/>
-      <c r="D23" s="117" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="116"/>
+      <c r="A23" s="118" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="119"/>
+      <c r="C23" s="121"/>
+      <c r="D23" s="140" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="119"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="121"/>
       <c r="I23" s="43" t="s">
         <v>25</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="124" t="s">
+      <c r="A24" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="115"/>
-      <c r="C24" s="116"/>
+      <c r="B24" s="119"/>
+      <c r="C24" s="121"/>
       <c r="D24" s="43" t="s">
         <v>27</v>
       </c>
@@ -15106,67 +15091,46 @@
       <c r="G24" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H24" s="125" t="s">
+      <c r="H24" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="115"/>
-      <c r="J24" s="118"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="120"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="114">
+      <c r="A25" s="142">
         <v>2</v>
       </c>
-      <c r="B25" s="115"/>
-      <c r="C25" s="116"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="121"/>
       <c r="D25" s="42" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F25" s="41"/>
       <c r="G25" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="H25" s="117"/>
-      <c r="I25" s="115"/>
-      <c r="J25" s="118"/>
+        <v>94</v>
+      </c>
+      <c r="H25" s="140"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="120"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A26" s="119"/>
-      <c r="B26" s="120"/>
-      <c r="C26" s="121"/>
+      <c r="A26" s="143"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="145"/>
       <c r="D26" s="40"/>
       <c r="E26" s="40"/>
       <c r="F26" s="39"/>
       <c r="G26" s="39"/>
-      <c r="H26" s="122"/>
-      <c r="I26" s="120"/>
-      <c r="J26" s="123"/>
+      <c r="H26" s="146"/>
+      <c r="I26" s="144"/>
+      <c r="J26" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A7:J13"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="H26:J26"/>
     <mergeCell ref="D19:H19"/>
@@ -15181,6 +15145,27 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/プロジェクト型演習_成果物_TasBo_登録.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_登録.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\新しいフォルダー (4)\新しいフォルダー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AE1639-2068-4DB4-931F-378E08F0FC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{A7194389-4A27-4C3F-BB45-2473C269D49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="109">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -368,71 +369,10 @@
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>ユーザがシステムにログインしていること</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
     <t>ユースケース名</t>
-    <rPh sb="44" eb="45">
-      <t>ナイ</t>
+    <rPh sb="0" eb="7">
+      <t>ナイナイミチャクシュチャクシュチュウカンリョウ</t>
     </rPh>
-    <rPh sb="74" eb="75">
-      <t>ナイ</t>
-    </rPh>
-    <rPh sb="76" eb="79">
-      <t>ミチャクシュ</t>
-    </rPh>
-    <rPh sb="80" eb="83">
-      <t>チャクシュチュウ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>カンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>1.ユーザはタスク登録画面を表示する。
-2.システムはデータベースからカテゴリ情報、担当者情報、ステータス情報を取得し、各プルダウンに表示する。
-3.ユーザはタスク名を入力する。
-4. ユーザはカテゴリのプルダウン内のいずれかを選択する。
- ・カテゴリプルダウンは m_category テーブルの情報を表示する。
- ・担当者プルダウンは m_user テーブルの情報を表示する。
- ・ステータスプルダウンは m_status テーブルの情報を表示する。
-5.ユーザは期限日を入力する。
-6.ユーザは登録ボタンを押下する。
-7.システムは入力内容をチェックする。
-8.システムはタスク情報を登録する。
-9.システムは登録完了画面へページへ遷移する。</t>
-    <rPh sb="429" eb="431">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="436" eb="438">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>成功時 : タスク情報が登録されている。/登録完了画面が表示されている。
-失敗時 : タスク情報は登録されていない。/登録失敗画面が表示されている。</t>
-    <rPh sb="61" eb="63">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="304" eb="306">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="318" eb="320">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>E1. タスク情報の登録に失敗した場合（基本フロー10から分岐）
-a. システムは登録処理の失敗を検出する。
-b. システムは登録失敗画面を表示する。
-E2. 入力値が文字数制限を超えている場合（基本フロー9から分岐）
-a. システムは文字数制限超過を検出する。
-b. システムは登録処理を中止する。
-c. システムは登録失敗画面を表示する。</t>
     <phoneticPr fontId="9"/>
   </si>
   <si>
@@ -458,17 +398,6 @@
   </si>
   <si>
     <t>submit</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>A1. 必須項目が未入力の場合（基本フロー9から分岐）
-a. システムは未入力項目を検出する。
-b. システムは該当項目のエラーメッセージ「このフィールドに入力してください。」を表示する。
-c. システムはタスク登録画面を再表示する。
-A2. ユーザがクリアボタンを押下した場合（基本フロー3～8から分岐）
-a. ユーザはクリアボタンを押下する。
-b. システムは入力済みの項目を初期状態に戻す。
-c. システムはタスク登録画面を再表示する。</t>
     <phoneticPr fontId="9"/>
   </si>
   <si>
@@ -516,6 +445,64 @@
   </si>
   <si>
     <t>GET</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>1.ユーザはタスク登録画面を表示する。
+2.システムはデータベースからカテゴリ情報、担当者情報、ステータス情報を取得し、各プルダウンに表示する。
+3.ユーザはタスク名を入力する。
+4.ユーザはカテゴリのプルダウン内のいずれかを選択する。
+5.ユーザは期限日を入力する。
+6.ユーザは担当者のプルダウン内のいずれかを選択する。
+7.ユーザはステータスのプルダウン内のいずれかを選択する。
+8.ユーザはメモを入力する。
+9.ユーザは登録ボタンを押下する。
+10.システムは入力内容をチェックする。
+11.システムはタスク情報を登録する。
+12.システムは登録完了画面へ遷移する。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>A1. 必須項目が未入力の場合（基本フロー10から分岐）
+a. システムは未入力項目を検出する。
+b. システムは該当項目のエラーメッセージ「このフィールドに入力してください。」を表示する。
+c. システムはタスク登録画面を再表示する。
+A2. ユーザがクリアボタンを押下した場合（基本フロー3～9から分岐）
+a. ユーザはクリアボタンを押下する。
+b. システムは入力済みの項目を初期状態に戻す。
+c. システムはタスク登録画面を再表示する。
+A3. 入力値が文字数制限を超えている場合（基本フロー10から分岐）
+a. システムは文字数制限超過を検出する。
+b. システムは「入力可能文字数を超えています。」と表示する。
+c. システムはタスク登録画面を再表示する。
+A4. 期限日に過去日が入力されている場合（基本フロー10から分岐）
+a. システムは期限日が当日以前であることを検出する。
+b. システムは「期限日には未来日を入力してください。」と表示する。
+c. システムはタスク登録画面を再表示する。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>E1. タスク情報の登録に失敗した場合（基本フロー11から分岐）
+a. システムは登録処理の失敗を検出する。
+b. システムは登録失敗画面を表示する。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>成功時 ： タスク情報が登録されている。/登録完了画面が表示されている。
+失敗時 ： タスク情報は登録されていない。/登録失敗画面が表示されている。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>・カテゴリプルダウンは m_category テーブルの情報を表示する。
+・担当者プルダウンは m_user テーブルの情報を表示する。
+・ステータスプルダウンは m_status テーブルの情報を表示する。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>ユーザがシステムにログインしていること
+m_category テーブルにカテゴリ情報が登録されていること。
+m_user テーブルに担当者情報が登録されていること。
+m_status テーブルにステータス情報が登録されていること。</t>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -1407,20 +1394,185 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1436,48 +1588,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1487,134 +1603,35 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1622,47 +1639,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2964,85 +2951,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="76"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="59"/>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="59"/>
-      <c r="L4" s="59"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3062,50 +3049,50 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="90" t="s">
+      <c r="E8" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="59"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="62"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="84" t="s">
+      <c r="G13" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="86"/>
-      <c r="I13" s="91">
+      <c r="H13" s="42"/>
+      <c r="I13" s="78">
         <v>46175</v>
       </c>
-      <c r="J13" s="85"/>
-      <c r="K13" s="86"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="42"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="84" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="86"/>
-      <c r="I14" s="91">
+      <c r="G14" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" s="42"/>
+      <c r="I14" s="78">
         <v>46189</v>
       </c>
-      <c r="J14" s="85"/>
-      <c r="K14" s="86"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="42"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="84"/>
-      <c r="H15" s="86"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="85"/>
-      <c r="K15" s="86"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="42"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3114,13 +3101,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="87" t="s">
+      <c r="G17" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="59"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="59"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4134,16 +4121,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="64" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="66" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="65"/>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="66" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="65"/>
@@ -4158,192 +4145,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="66" t="s">
+      <c r="A2" s="61"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="70">
+      <c r="G2" s="50"/>
+      <c r="H2" s="108">
         <v>46175</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="40"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="41"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="42"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="46" t="s">
+      <c r="A5" s="98" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="99"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="48"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="102"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="52" t="s">
+      <c r="B6" s="80"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="54"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="91"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52" t="s">
+      <c r="B7" s="80"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="54"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="49" t="s">
+      <c r="E7" s="90"/>
+      <c r="F7" s="90"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="91"/>
+    </row>
+    <row r="8" spans="1:10" ht="69" customHeight="1">
+      <c r="A8" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="71" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="78"/>
-      <c r="I8" s="78"/>
-      <c r="J8" s="79"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="82" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="84"/>
     </row>
     <row r="9" spans="1:10" ht="192.75" customHeight="1">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="71" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="79"/>
-    </row>
-    <row r="10" spans="1:10" ht="147.75" customHeight="1">
-      <c r="A10" s="81"/>
-      <c r="B10" s="83" t="s">
+      <c r="C9" s="81"/>
+      <c r="D9" s="82" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="84"/>
+    </row>
+    <row r="10" spans="1:10" ht="274.5" customHeight="1">
+      <c r="A10" s="93"/>
+      <c r="B10" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="79"/>
-    </row>
-    <row r="11" spans="1:10" ht="127.5" customHeight="1">
-      <c r="A11" s="82"/>
-      <c r="B11" s="83" t="s">
+      <c r="C10" s="81"/>
+      <c r="D10" s="82" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="84"/>
+    </row>
+    <row r="11" spans="1:10" ht="68.25" customHeight="1">
+      <c r="A11" s="94"/>
+      <c r="B11" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="71" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="79"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="82" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="84"/>
     </row>
     <row r="12" spans="1:10" ht="66.75" customHeight="1">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="71" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="79"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="72" t="s">
+      <c r="B12" s="80"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="84"/>
+    </row>
+    <row r="13" spans="1:10" ht="63.75" customHeight="1" thickBot="1">
+      <c r="A13" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="76"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="77"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="122" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="88"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="89"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5334,6 +5323,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5349,18 +5350,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5379,16 +5368,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="64" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="66" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="65"/>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="66" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="65"/>
@@ -5403,40 +5392,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="40"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="41"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="42"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6792,16 +6781,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="64" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="66" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="65"/>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="66" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="65"/>
@@ -6816,48 +6805,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="66" t="s">
+      <c r="A2" s="61"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="93">
+      <c r="G2" s="50"/>
+      <c r="H2" s="109">
         <v>46175</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="40"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="41"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="42"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8210,16 +8199,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="64" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="66" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="65"/>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="66" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="65"/>
@@ -8234,190 +8223,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="66" t="s">
+      <c r="A2" s="61"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="106">
+      <c r="G2" s="50"/>
+      <c r="H2" s="53">
         <v>46175</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="40"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="41"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="58"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="41"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="97"/>
+      <c r="B5" s="64"/>
       <c r="C5" s="65"/>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="99"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="68"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="94"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="45"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="100"/>
-      <c r="B7" s="101"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="102"/>
+      <c r="A7" s="69"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="71"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="58"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="103"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="72"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="58"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="103"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="72"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="58"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="103"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="58"/>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="103"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="72"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="58"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="103"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="72"/>
     </row>
     <row r="13" spans="1:10" ht="93" customHeight="1">
-      <c r="A13" s="58"/>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="103"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="72"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="98" t="s">
+      <c r="A14" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="85"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
-      <c r="H14" s="85"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="94"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="45"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="85"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="52" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" s="85"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="85"/>
-      <c r="H15" s="86"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="42"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
@@ -8426,11 +8415,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="98" t="s">
+      <c r="A16" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="85"/>
-      <c r="C16" s="86"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="42"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -8443,18 +8432,18 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="104" t="s">
+      <c r="H16" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="85"/>
-      <c r="J16" s="94"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="45"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="95">
+      <c r="A17" s="46">
         <v>1</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="86"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="42"/>
       <c r="D17" s="17" t="s">
         <v>71</v>
       </c>
@@ -8467,18 +8456,18 @@
       <c r="G17" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="52" t="s">
-        <v>102</v>
-      </c>
-      <c r="I17" s="85"/>
-      <c r="J17" s="94"/>
+      <c r="H17" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" s="41"/>
+      <c r="J17" s="45"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="95">
+      <c r="A18" s="46">
         <v>2</v>
       </c>
-      <c r="B18" s="85"/>
-      <c r="C18" s="86"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="17" t="s">
         <v>75</v>
       </c>
@@ -8489,20 +8478,20 @@
         <v>81</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="H18" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="85"/>
-      <c r="J18" s="94"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="45"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="95">
+      <c r="A19" s="46">
         <v>3</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="86"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="42"/>
       <c r="D19" s="17" t="s">
         <v>76</v>
       </c>
@@ -8515,18 +8504,18 @@
       <c r="G19" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="85"/>
-      <c r="J19" s="94"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="45"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="95">
+      <c r="A20" s="46">
         <v>4</v>
       </c>
-      <c r="B20" s="85"/>
-      <c r="C20" s="86"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="17" t="s">
         <v>79</v>
       </c>
@@ -8534,23 +8523,23 @@
         <v>80</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="H20" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I20" s="85"/>
-      <c r="J20" s="94"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="45"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="95">
+      <c r="A21" s="46">
         <v>5</v>
       </c>
-      <c r="B21" s="85"/>
-      <c r="C21" s="86"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="17" t="s">
         <v>77</v>
       </c>
@@ -8558,153 +8547,153 @@
         <v>80</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="H21" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="H21" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I21" s="85"/>
-      <c r="J21" s="94"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="45"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="100">
+      <c r="A22" s="69">
         <v>6</v>
       </c>
-      <c r="B22" s="101"/>
-      <c r="C22" s="67"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="50"/>
       <c r="D22" s="36" t="s">
         <v>78</v>
       </c>
       <c r="E22" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="118" t="s">
+      <c r="F22" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="G22" s="118" t="s">
+      <c r="G22" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="H22" s="52" t="s">
+      <c r="H22" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I22" s="85"/>
-      <c r="J22" s="94"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="45"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="121">
+      <c r="A23" s="47">
         <v>7</v>
       </c>
-      <c r="B23" s="122"/>
-      <c r="C23" s="122"/>
-      <c r="D23" s="119" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="119" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="120" t="s">
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="G23" s="120" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" s="52" t="s">
+      <c r="G23" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="H23" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I23" s="85"/>
-      <c r="J23" s="94"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="45"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="121">
+      <c r="A24" s="47">
         <v>8</v>
       </c>
-      <c r="B24" s="122"/>
-      <c r="C24" s="122"/>
-      <c r="D24" s="119" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="119" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="120" t="s">
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="G24" s="120" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="52" t="s">
+      <c r="G24" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="85"/>
-      <c r="J24" s="94"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="45"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="121">
+      <c r="A25" s="47">
         <v>9</v>
       </c>
-      <c r="B25" s="122"/>
-      <c r="C25" s="122"/>
-      <c r="D25" s="119" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="119" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="120" t="s">
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="G25" s="120" t="s">
-        <v>105</v>
-      </c>
-      <c r="H25" s="52" t="s">
+      <c r="G25" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="H25" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I25" s="85"/>
-      <c r="J25" s="94"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="45"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="98" t="s">
+      <c r="A26" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="85"/>
-      <c r="C26" s="85"/>
-      <c r="D26" s="85"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="94"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="45"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="98" t="s">
+      <c r="A27" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="85"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="86"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="42"/>
       <c r="I27" s="15" t="s">
         <v>24</v>
       </c>
       <c r="J27" s="16" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="98" t="s">
+      <c r="A28" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="85"/>
-      <c r="C28" s="86"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="42"/>
       <c r="D28" s="15" t="s">
         <v>26</v>
       </c>
@@ -8717,33 +8706,33 @@
       <c r="G28" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H28" s="104" t="s">
+      <c r="H28" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="I28" s="85"/>
-      <c r="J28" s="94"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="45"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="95">
+      <c r="A29" s="46">
         <v>1</v>
       </c>
-      <c r="B29" s="85"/>
-      <c r="C29" s="86"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="42"/>
       <c r="D29" s="17" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F29" s="18" t="s">
         <v>74</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="H29" s="52"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="94"/>
+        <v>100</v>
+      </c>
+      <c r="H29" s="43"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="45"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9720,22 +9709,16 @@
     <row r="1002" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9752,16 +9735,22 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9781,182 +9770,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="64" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
       <c r="J1" s="65"/>
-      <c r="K1" s="64" t="s">
+      <c r="K1" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
       <c r="N1" s="65"/>
-      <c r="O1" s="64" t="s">
+      <c r="O1" s="66" t="s">
         <v>5</v>
       </c>
       <c r="P1" s="65"/>
-      <c r="Q1" s="64" t="s">
+      <c r="Q1" s="66" t="s">
         <v>6</v>
       </c>
       <c r="R1" s="65"/>
-      <c r="S1" s="64" t="s">
+      <c r="S1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="99"/>
+      <c r="T1" s="68"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="102"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="71"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="59"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="103"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="72"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="69"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="105"/>
+      <c r="M4" s="105"/>
+      <c r="N4" s="106"/>
+      <c r="O4" s="107"/>
+      <c r="P4" s="106"/>
+      <c r="Q4" s="107"/>
+      <c r="R4" s="106"/>
+      <c r="S4" s="107"/>
       <c r="T4" s="116"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
       <c r="F5" s="65"/>
-      <c r="G5" s="46" t="s">
+      <c r="G5" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="97"/>
-      <c r="M5" s="97"/>
-      <c r="N5" s="97"/>
-      <c r="O5" s="97"/>
-      <c r="P5" s="97"/>
-      <c r="Q5" s="97"/>
-      <c r="R5" s="97"/>
-      <c r="S5" s="97"/>
-      <c r="T5" s="99"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="64"/>
+      <c r="Q5" s="64"/>
+      <c r="R5" s="64"/>
+      <c r="S5" s="64"/>
+      <c r="T5" s="68"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="52" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="85"/>
-      <c r="K6" s="85"/>
-      <c r="L6" s="85"/>
-      <c r="M6" s="85"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="85"/>
-      <c r="P6" s="85"/>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85"/>
-      <c r="T6" s="94"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="45"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="98" t="s">
+      <c r="A7" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="52" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="85"/>
-      <c r="K7" s="85"/>
-      <c r="L7" s="85"/>
-      <c r="M7" s="85"/>
-      <c r="N7" s="85"/>
-      <c r="O7" s="85"/>
-      <c r="P7" s="85"/>
-      <c r="Q7" s="85"/>
-      <c r="R7" s="85"/>
-      <c r="S7" s="85"/>
-      <c r="T7" s="94"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="45"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10155,37 +10144,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="86"/>
-      <c r="C15" s="115" t="s">
+      <c r="B15" s="42"/>
+      <c r="C15" s="119" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="86"/>
-      <c r="E15" s="104" t="s">
+      <c r="D15" s="42"/>
+      <c r="E15" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="86"/>
-      <c r="G15" s="104" t="s">
+      <c r="F15" s="42"/>
+      <c r="G15" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="85"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="104" t="s">
+      <c r="H15" s="41"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="86"/>
-      <c r="L15" s="104" t="s">
+      <c r="K15" s="42"/>
+      <c r="L15" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="M15" s="85"/>
-      <c r="N15" s="86"/>
-      <c r="O15" s="104" t="s">
+      <c r="M15" s="41"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="P15" s="85"/>
-      <c r="Q15" s="86"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="42"/>
       <c r="R15" s="15" t="s">
         <v>48</v>
       </c>
@@ -10197,37 +10186,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="107">
+      <c r="A16" s="117">
         <v>1</v>
       </c>
-      <c r="B16" s="86"/>
-      <c r="C16" s="108" t="s">
+      <c r="B16" s="42"/>
+      <c r="C16" s="118" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="86"/>
-      <c r="E16" s="108" t="s">
+      <c r="D16" s="42"/>
+      <c r="E16" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="86"/>
-      <c r="G16" s="114" t="s">
+      <c r="F16" s="42"/>
+      <c r="G16" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="85"/>
-      <c r="I16" s="86"/>
-      <c r="J16" s="114" t="s">
+      <c r="H16" s="41"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="110" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="86"/>
-      <c r="L16" s="112" t="s">
+      <c r="K16" s="42"/>
+      <c r="L16" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="85"/>
-      <c r="N16" s="86"/>
-      <c r="O16" s="112" t="s">
+      <c r="M16" s="41"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="85"/>
-      <c r="Q16" s="86"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="42"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
@@ -10239,37 +10228,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="107">
+      <c r="A17" s="117">
         <v>2</v>
       </c>
-      <c r="B17" s="86"/>
-      <c r="C17" s="108" t="s">
+      <c r="B17" s="42"/>
+      <c r="C17" s="118" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="86"/>
-      <c r="E17" s="108" t="s">
+      <c r="D17" s="42"/>
+      <c r="E17" s="118" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="86"/>
-      <c r="G17" s="114" t="s">
+      <c r="F17" s="42"/>
+      <c r="G17" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="85"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="114" t="s">
+      <c r="H17" s="41"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="K17" s="86"/>
-      <c r="L17" s="112" t="s">
+      <c r="K17" s="42"/>
+      <c r="L17" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="85"/>
-      <c r="N17" s="86"/>
-      <c r="O17" s="112" t="s">
+      <c r="M17" s="41"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="P17" s="85"/>
-      <c r="Q17" s="86"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="42"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31"/>
       <c r="T17" s="32"/>
@@ -10281,23 +10270,23 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="107"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="108"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="108"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="114"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="85"/>
-      <c r="N18" s="86"/>
-      <c r="O18" s="112"/>
-      <c r="P18" s="85"/>
-      <c r="Q18" s="86"/>
+      <c r="A18" s="117"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="110"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="114"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="41"/>
+      <c r="Q18" s="42"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
       <c r="T18" s="32"/>
@@ -10309,23 +10298,23 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="107"/>
-      <c r="B19" s="86"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="86"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="114"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="85"/>
-      <c r="N19" s="86"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="85"/>
-      <c r="Q19" s="86"/>
+      <c r="A19" s="117"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="114"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="114"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="42"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
       <c r="T19" s="32"/>
@@ -10337,23 +10326,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="107"/>
-      <c r="B20" s="86"/>
-      <c r="C20" s="108"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="108"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="112"/>
-      <c r="M20" s="85"/>
-      <c r="N20" s="86"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="85"/>
-      <c r="Q20" s="86"/>
+      <c r="A20" s="117"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="114"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="114"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="42"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -10365,23 +10354,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="107"/>
-      <c r="B21" s="86"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="86"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="86"/>
-      <c r="J21" s="114"/>
-      <c r="K21" s="86"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="85"/>
-      <c r="N21" s="86"/>
-      <c r="O21" s="112"/>
-      <c r="P21" s="85"/>
-      <c r="Q21" s="86"/>
+      <c r="A21" s="117"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="42"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -10393,23 +10382,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="107"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="108"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="86"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="85"/>
-      <c r="I22" s="86"/>
-      <c r="J22" s="114"/>
-      <c r="K22" s="86"/>
-      <c r="L22" s="112"/>
-      <c r="M22" s="85"/>
-      <c r="N22" s="86"/>
-      <c r="O22" s="112"/>
-      <c r="P22" s="85"/>
-      <c r="Q22" s="86"/>
+      <c r="A22" s="117"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="114"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="114"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="42"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -10421,23 +10410,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="107"/>
-      <c r="B23" s="86"/>
-      <c r="C23" s="108"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="86"/>
-      <c r="G23" s="114"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="86"/>
-      <c r="J23" s="114"/>
-      <c r="K23" s="86"/>
-      <c r="L23" s="112"/>
-      <c r="M23" s="85"/>
-      <c r="N23" s="86"/>
-      <c r="O23" s="112"/>
-      <c r="P23" s="85"/>
-      <c r="Q23" s="86"/>
+      <c r="A23" s="117"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="114"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="114"/>
+      <c r="P23" s="41"/>
+      <c r="Q23" s="42"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -10449,23 +10438,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="107"/>
-      <c r="B24" s="86"/>
-      <c r="C24" s="108"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="108"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="114"/>
-      <c r="H24" s="85"/>
-      <c r="I24" s="86"/>
-      <c r="J24" s="114"/>
-      <c r="K24" s="86"/>
-      <c r="L24" s="112"/>
-      <c r="M24" s="85"/>
-      <c r="N24" s="86"/>
-      <c r="O24" s="112"/>
-      <c r="P24" s="85"/>
-      <c r="Q24" s="86"/>
+      <c r="A24" s="117"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="110"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="114"/>
+      <c r="M24" s="41"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="114"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="42"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -10477,23 +10466,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="107"/>
-      <c r="B25" s="86"/>
-      <c r="C25" s="108"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="114"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="114"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="112"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="86"/>
-      <c r="O25" s="112"/>
-      <c r="P25" s="85"/>
-      <c r="Q25" s="86"/>
+      <c r="A25" s="117"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="114"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="42"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -10505,23 +10494,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="107"/>
-      <c r="B26" s="86"/>
-      <c r="C26" s="108"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="114"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="114"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="112"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="86"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="85"/>
-      <c r="Q26" s="86"/>
+      <c r="A26" s="117"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="118"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="110"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="114"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="42"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -10533,23 +10522,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="107"/>
-      <c r="B27" s="86"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="86"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="86"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="112"/>
-      <c r="M27" s="85"/>
-      <c r="N27" s="86"/>
-      <c r="O27" s="112"/>
-      <c r="P27" s="85"/>
-      <c r="Q27" s="86"/>
+      <c r="A27" s="117"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="118"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="114"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="42"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -10561,23 +10550,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="107"/>
-      <c r="B28" s="86"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="85"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="112"/>
-      <c r="M28" s="85"/>
-      <c r="N28" s="86"/>
-      <c r="O28" s="112"/>
-      <c r="P28" s="85"/>
-      <c r="Q28" s="86"/>
+      <c r="A28" s="117"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="118"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="110"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="114"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="114"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="42"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -10589,23 +10578,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="107"/>
-      <c r="B29" s="86"/>
-      <c r="C29" s="108"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="114"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="86"/>
-      <c r="J29" s="114"/>
-      <c r="K29" s="86"/>
-      <c r="L29" s="112"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="86"/>
-      <c r="O29" s="112"/>
-      <c r="P29" s="85"/>
-      <c r="Q29" s="86"/>
+      <c r="A29" s="117"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="118"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="114"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="42"/>
+      <c r="O29" s="114"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="42"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -10617,23 +10606,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="107"/>
-      <c r="B30" s="86"/>
-      <c r="C30" s="108"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="86"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="112"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="86"/>
-      <c r="O30" s="112"/>
-      <c r="P30" s="85"/>
-      <c r="Q30" s="86"/>
+      <c r="A30" s="117"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="118"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="114"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="42"/>
+      <c r="O30" s="114"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="42"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -10645,23 +10634,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="109"/>
-      <c r="B31" s="110"/>
-      <c r="C31" s="111"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="111"/>
-      <c r="F31" s="110"/>
-      <c r="G31" s="117"/>
-      <c r="H31" s="105"/>
-      <c r="I31" s="110"/>
-      <c r="J31" s="117"/>
-      <c r="K31" s="110"/>
-      <c r="L31" s="113"/>
-      <c r="M31" s="105"/>
-      <c r="N31" s="110"/>
-      <c r="O31" s="113"/>
-      <c r="P31" s="105"/>
-      <c r="Q31" s="110"/>
+      <c r="A31" s="120"/>
+      <c r="B31" s="113"/>
+      <c r="C31" s="121"/>
+      <c r="D31" s="113"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="113"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="113"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="115"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="113"/>
+      <c r="O31" s="115"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="113"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -11659,62 +11648,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11739,62 +11728,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/プロジェクト型演習_成果物_TasBo_登録.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_登録.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\新しいフォルダー (4)\新しいフォルダー\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TasBo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90194BDF-5A5E-4D2C-9B25-F6B85BA5D2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2127FAC4-4B16-459B-869C-F5EDA3C75049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="141">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -737,10 +737,6 @@
     <rPh sb="14" eb="16">
       <t>トウロク</t>
     </rPh>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>2026\06/19</t>
     <phoneticPr fontId="20"/>
   </si>
 </sst>
@@ -1846,7 +1842,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2052,10 +2048,370 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="60" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="61" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="61" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="72" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="72" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="61" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="59" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="73" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="75" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="76" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="73" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="75" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="76" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="75" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2064,364 +2420,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="76" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="75" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="76" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="73" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="75" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="76" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="61" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="72" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="72" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="61" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="59" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="60" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="61" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="59" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="69" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3882,85 +3881,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="105" t="s">
+      <c r="C2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="106"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="106"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="106"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="104"/>
-      <c r="O3" s="104"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="104"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="104"/>
-      <c r="N4" s="104"/>
-      <c r="O4" s="104"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="83"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="104"/>
-      <c r="O5" s="104"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="83"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
-      <c r="F6" s="104"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="104"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="104"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="104"/>
-      <c r="O6" s="104"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="83"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3980,50 +3979,50 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="107" t="s">
+      <c r="E8" s="86" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="104"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="104"/>
-      <c r="M8" s="104"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="83"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="100" t="s">
+      <c r="G13" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="102"/>
-      <c r="I13" s="108">
+      <c r="H13" s="81"/>
+      <c r="I13" s="87">
         <v>46175</v>
       </c>
-      <c r="J13" s="101"/>
-      <c r="K13" s="102"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="81"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="100" t="s">
+      <c r="G14" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="H14" s="102"/>
-      <c r="I14" s="108">
+      <c r="H14" s="81"/>
+      <c r="I14" s="87">
         <v>46189</v>
       </c>
-      <c r="J14" s="101"/>
-      <c r="K14" s="102"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="81"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="100"/>
-      <c r="H15" s="102"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="102"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="81"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -4032,13 +4031,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="103" t="s">
+      <c r="G17" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="104"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="104"/>
-      <c r="K17" s="104"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="83"/>
+      <c r="K17" s="83"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -5052,19 +5051,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="148" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="149"/>
-      <c r="F1" s="148" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="149"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -5076,194 +5075,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="150" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="151"/>
-      <c r="F2" s="150" t="s">
+      <c r="E2" s="117"/>
+      <c r="F2" s="116" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="151"/>
-      <c r="H2" s="154">
+      <c r="G2" s="117"/>
+      <c r="H2" s="120">
         <v>46175</v>
       </c>
-      <c r="I2" s="128" t="s">
+      <c r="I2" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="131"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="143"/>
-      <c r="B3" s="104"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="132"/>
+      <c r="A3" s="109"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="145"/>
-      <c r="B4" s="146"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="133"/>
+      <c r="A4" s="111"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="94" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="137" t="s">
+      <c r="B5" s="95"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="138"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="138"/>
-      <c r="H5" s="138"/>
-      <c r="I5" s="138"/>
-      <c r="J5" s="139"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="99"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="109" t="s">
+      <c r="A6" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="121" t="s">
+      <c r="B6" s="101"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="123"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="105"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="109" t="s">
+      <c r="A7" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="110"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="121" t="s">
+      <c r="B7" s="101"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="123"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="105"/>
     </row>
     <row r="8" spans="1:10" ht="69" customHeight="1">
-      <c r="A8" s="109" t="s">
+      <c r="A8" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="110"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="112" t="s">
+      <c r="B8" s="101"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="121" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="113"/>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="114"/>
+      <c r="E8" s="122"/>
+      <c r="F8" s="122"/>
+      <c r="G8" s="122"/>
+      <c r="H8" s="122"/>
+      <c r="I8" s="122"/>
+      <c r="J8" s="123"/>
     </row>
     <row r="9" spans="1:10" ht="192.75" customHeight="1">
-      <c r="A9" s="124" t="s">
+      <c r="A9" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="127" t="s">
+      <c r="B9" s="133" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="112" t="s">
+      <c r="C9" s="102"/>
+      <c r="D9" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="113"/>
-      <c r="F9" s="113"/>
-      <c r="G9" s="113"/>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113"/>
-      <c r="J9" s="114"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="122"/>
+      <c r="G9" s="122"/>
+      <c r="H9" s="122"/>
+      <c r="I9" s="122"/>
+      <c r="J9" s="123"/>
     </row>
     <row r="10" spans="1:10" ht="274.5" customHeight="1">
-      <c r="A10" s="125"/>
-      <c r="B10" s="127" t="s">
+      <c r="A10" s="131"/>
+      <c r="B10" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="112" t="s">
+      <c r="C10" s="102"/>
+      <c r="D10" s="121" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="113"/>
-      <c r="F10" s="113"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="114"/>
+      <c r="E10" s="122"/>
+      <c r="F10" s="122"/>
+      <c r="G10" s="122"/>
+      <c r="H10" s="122"/>
+      <c r="I10" s="122"/>
+      <c r="J10" s="123"/>
     </row>
     <row r="11" spans="1:10" ht="68.25" customHeight="1">
-      <c r="A11" s="126"/>
-      <c r="B11" s="127" t="s">
+      <c r="A11" s="132"/>
+      <c r="B11" s="133" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="111"/>
-      <c r="D11" s="112" t="s">
+      <c r="C11" s="102"/>
+      <c r="D11" s="121" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="113"/>
-      <c r="F11" s="113"/>
-      <c r="G11" s="113"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="113"/>
-      <c r="J11" s="114"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="122"/>
+      <c r="H11" s="122"/>
+      <c r="I11" s="122"/>
+      <c r="J11" s="123"/>
     </row>
     <row r="12" spans="1:10" ht="66.75" customHeight="1">
-      <c r="A12" s="109" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="110"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="112" t="s">
+      <c r="B12" s="101"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="121" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="113"/>
-      <c r="F12" s="113"/>
-      <c r="G12" s="113"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="113"/>
-      <c r="J12" s="114"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="123"/>
     </row>
     <row r="13" spans="1:10" ht="63.75" customHeight="1" thickBot="1">
-      <c r="A13" s="115" t="s">
+      <c r="A13" s="124" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="116"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="118" t="s">
+      <c r="B13" s="125"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="119"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="119"/>
-      <c r="H13" s="119"/>
-      <c r="I13" s="119"/>
-      <c r="J13" s="120"/>
+      <c r="E13" s="128"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="128"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="128"/>
+      <c r="J13" s="129"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6254,18 +6253,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -6281,6 +6268,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6299,19 +6298,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="134" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="148" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="149"/>
-      <c r="F1" s="148" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="149"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -6323,40 +6322,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="131"/>
+      <c r="A2" s="109"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="143"/>
-      <c r="B3" s="104"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="132"/>
+      <c r="A3" s="109"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="145"/>
-      <c r="B4" s="146"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="133"/>
+      <c r="A4" s="111"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7712,19 +7711,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="148" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="149"/>
-      <c r="F1" s="148" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="149"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7736,48 +7735,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="150" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="151"/>
-      <c r="F2" s="150" t="s">
+      <c r="E2" s="117"/>
+      <c r="F2" s="116" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="151"/>
-      <c r="H2" s="156">
+      <c r="G2" s="117"/>
+      <c r="H2" s="135">
         <v>46175</v>
       </c>
-      <c r="I2" s="128" t="s">
+      <c r="I2" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="131"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="143"/>
-      <c r="B3" s="104"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="132"/>
+      <c r="A3" s="109"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="145"/>
-      <c r="B4" s="146"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="133"/>
+      <c r="A4" s="111"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -9130,19 +9129,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="148" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="149"/>
-      <c r="F1" s="148" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="149"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -9154,190 +9153,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="150" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="151"/>
-      <c r="F2" s="150" t="s">
+      <c r="E2" s="117"/>
+      <c r="F2" s="116" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="151"/>
-      <c r="H2" s="163">
+      <c r="G2" s="117"/>
+      <c r="H2" s="149">
         <v>46175</v>
       </c>
-      <c r="I2" s="128" t="s">
+      <c r="I2" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="131"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="143"/>
-      <c r="B3" s="104"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="132"/>
+      <c r="A3" s="109"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="143"/>
-      <c r="B4" s="104"/>
-      <c r="C4" s="144"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="144"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="132"/>
+      <c r="A4" s="109"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="92"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="164" t="s">
+      <c r="A5" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="165"/>
-      <c r="C5" s="149"/>
-      <c r="D5" s="138" t="s">
+      <c r="B5" s="141"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="165"/>
-      <c r="F5" s="165"/>
-      <c r="G5" s="165"/>
-      <c r="H5" s="165"/>
-      <c r="I5" s="165"/>
-      <c r="J5" s="166"/>
+      <c r="E5" s="141"/>
+      <c r="F5" s="141"/>
+      <c r="G5" s="141"/>
+      <c r="H5" s="141"/>
+      <c r="I5" s="141"/>
+      <c r="J5" s="145"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="101"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="101"/>
-      <c r="J6" s="159"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="136"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="167"/>
-      <c r="B7" s="168"/>
-      <c r="C7" s="168"/>
-      <c r="D7" s="168"/>
-      <c r="E7" s="168"/>
-      <c r="F7" s="168"/>
-      <c r="G7" s="168"/>
-      <c r="H7" s="168"/>
-      <c r="I7" s="168"/>
-      <c r="J7" s="169"/>
+      <c r="A7" s="138"/>
+      <c r="B7" s="139"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="139"/>
+      <c r="E7" s="139"/>
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="146"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="143"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="170"/>
+      <c r="A8" s="109"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="147"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="143"/>
-      <c r="B9" s="104"/>
-      <c r="C9" s="104"/>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="170"/>
+      <c r="A9" s="109"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="147"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="143"/>
-      <c r="B10" s="104"/>
-      <c r="C10" s="104"/>
-      <c r="D10" s="104"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="170"/>
+      <c r="A10" s="109"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="147"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="143"/>
-      <c r="B11" s="104"/>
-      <c r="C11" s="104"/>
-      <c r="D11" s="104"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="170"/>
+      <c r="A11" s="109"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="147"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="143"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="170"/>
+      <c r="A12" s="109"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="147"/>
     </row>
     <row r="13" spans="1:10" ht="93" customHeight="1">
-      <c r="A13" s="143"/>
-      <c r="B13" s="104"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="104"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="170"/>
+      <c r="A13" s="109"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="147"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="157" t="s">
+      <c r="A14" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="101"/>
-      <c r="C14" s="101"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="101"/>
-      <c r="G14" s="101"/>
-      <c r="H14" s="101"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="159"/>
+      <c r="B14" s="80"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="136"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="157" t="s">
+      <c r="A15" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="101"/>
-      <c r="C15" s="102"/>
-      <c r="D15" s="121" t="s">
+      <c r="B15" s="80"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="102"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="81"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
@@ -9346,11 +9345,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="101"/>
-      <c r="C16" s="102"/>
+      <c r="B16" s="80"/>
+      <c r="C16" s="81"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -9363,18 +9362,18 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="158" t="s">
+      <c r="H16" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="101"/>
-      <c r="J16" s="159"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="136"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="160">
+      <c r="A17" s="137">
         <v>1</v>
       </c>
-      <c r="B17" s="101"/>
-      <c r="C17" s="102"/>
+      <c r="B17" s="80"/>
+      <c r="C17" s="81"/>
       <c r="D17" s="17" t="s">
         <v>71</v>
       </c>
@@ -9387,18 +9386,18 @@
       <c r="G17" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="121" t="s">
+      <c r="H17" s="103" t="s">
         <v>97</v>
       </c>
-      <c r="I17" s="101"/>
-      <c r="J17" s="159"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="136"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="160">
+      <c r="A18" s="137">
         <v>2</v>
       </c>
-      <c r="B18" s="101"/>
-      <c r="C18" s="102"/>
+      <c r="B18" s="80"/>
+      <c r="C18" s="81"/>
       <c r="D18" s="17" t="s">
         <v>75</v>
       </c>
@@ -9411,18 +9410,18 @@
       <c r="G18" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="121" t="s">
+      <c r="H18" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="101"/>
-      <c r="J18" s="159"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="136"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="160">
+      <c r="A19" s="137">
         <v>3</v>
       </c>
-      <c r="B19" s="101"/>
-      <c r="C19" s="102"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="81"/>
       <c r="D19" s="17" t="s">
         <v>76</v>
       </c>
@@ -9435,18 +9434,18 @@
       <c r="G19" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="H19" s="121" t="s">
+      <c r="H19" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="101"/>
-      <c r="J19" s="159"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="136"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="160">
+      <c r="A20" s="137">
         <v>4</v>
       </c>
-      <c r="B20" s="101"/>
-      <c r="C20" s="102"/>
+      <c r="B20" s="80"/>
+      <c r="C20" s="81"/>
       <c r="D20" s="17" t="s">
         <v>79</v>
       </c>
@@ -9459,18 +9458,18 @@
       <c r="G20" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="H20" s="121" t="s">
+      <c r="H20" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="I20" s="101"/>
-      <c r="J20" s="159"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="136"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="160">
+      <c r="A21" s="137">
         <v>5</v>
       </c>
-      <c r="B21" s="101"/>
-      <c r="C21" s="102"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="81"/>
       <c r="D21" s="17" t="s">
         <v>77</v>
       </c>
@@ -9483,18 +9482,18 @@
       <c r="G21" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="H21" s="121" t="s">
+      <c r="H21" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="I21" s="101"/>
-      <c r="J21" s="159"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="136"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="167">
+      <c r="A22" s="138">
         <v>6</v>
       </c>
-      <c r="B22" s="168"/>
-      <c r="C22" s="151"/>
+      <c r="B22" s="139"/>
+      <c r="C22" s="117"/>
       <c r="D22" s="36" t="s">
         <v>78</v>
       </c>
@@ -9507,18 +9506,18 @@
       <c r="G22" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="H22" s="121" t="s">
+      <c r="H22" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="I22" s="101"/>
-      <c r="J22" s="159"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="136"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="161">
+      <c r="A23" s="142">
         <v>7</v>
       </c>
-      <c r="B23" s="162"/>
-      <c r="C23" s="162"/>
+      <c r="B23" s="143"/>
+      <c r="C23" s="143"/>
       <c r="D23" s="38" t="s">
         <v>90</v>
       </c>
@@ -9531,18 +9530,18 @@
       <c r="G23" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="H23" s="121" t="s">
+      <c r="H23" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="I23" s="101"/>
-      <c r="J23" s="159"/>
+      <c r="I23" s="80"/>
+      <c r="J23" s="136"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="161">
+      <c r="A24" s="142">
         <v>8</v>
       </c>
-      <c r="B24" s="162"/>
-      <c r="C24" s="162"/>
+      <c r="B24" s="143"/>
+      <c r="C24" s="143"/>
       <c r="D24" s="38" t="s">
         <v>98</v>
       </c>
@@ -9555,18 +9554,18 @@
       <c r="G24" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="H24" s="121" t="s">
+      <c r="H24" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="101"/>
-      <c r="J24" s="159"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="136"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="161">
+      <c r="A25" s="142">
         <v>9</v>
       </c>
-      <c r="B25" s="162"/>
-      <c r="C25" s="162"/>
+      <c r="B25" s="143"/>
+      <c r="C25" s="143"/>
       <c r="D25" s="38" t="s">
         <v>100</v>
       </c>
@@ -9579,39 +9578,39 @@
       <c r="G25" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="H25" s="121" t="s">
+      <c r="H25" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="I25" s="101"/>
-      <c r="J25" s="159"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="136"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="157" t="s">
+      <c r="A26" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="101"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="101"/>
-      <c r="H26" s="101"/>
-      <c r="I26" s="101"/>
-      <c r="J26" s="159"/>
+      <c r="B26" s="80"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="136"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="157" t="s">
+      <c r="A27" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="101"/>
-      <c r="C27" s="102"/>
-      <c r="D27" s="121" t="s">
+      <c r="B27" s="80"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="103" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="101"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="101"/>
-      <c r="H27" s="102"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="80"/>
+      <c r="G27" s="80"/>
+      <c r="H27" s="81"/>
       <c r="I27" s="15" t="s">
         <v>24</v>
       </c>
@@ -9620,11 +9619,11 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="157" t="s">
+      <c r="A28" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="101"/>
-      <c r="C28" s="102"/>
+      <c r="B28" s="80"/>
+      <c r="C28" s="81"/>
       <c r="D28" s="15" t="s">
         <v>26</v>
       </c>
@@ -9637,18 +9636,18 @@
       <c r="G28" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H28" s="158" t="s">
+      <c r="H28" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="I28" s="101"/>
-      <c r="J28" s="159"/>
+      <c r="I28" s="80"/>
+      <c r="J28" s="136"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="160">
+      <c r="A29" s="137">
         <v>1</v>
       </c>
-      <c r="B29" s="101"/>
-      <c r="C29" s="102"/>
+      <c r="B29" s="80"/>
+      <c r="C29" s="81"/>
       <c r="D29" s="17" t="s">
         <v>100</v>
       </c>
@@ -9661,9 +9660,9 @@
       <c r="G29" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="H29" s="121"/>
-      <c r="I29" s="101"/>
-      <c r="J29" s="159"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="136"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10640,16 +10639,22 @@
     <row r="1002" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -10666,22 +10671,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H25:J25"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10701,182 +10700,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="106" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="148" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
-      <c r="J1" s="149"/>
-      <c r="K1" s="148" t="s">
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="165"/>
-      <c r="M1" s="165"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="148" t="s">
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="149"/>
-      <c r="Q1" s="148" t="s">
+      <c r="P1" s="115"/>
+      <c r="Q1" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="149"/>
-      <c r="S1" s="148" t="s">
+      <c r="R1" s="115"/>
+      <c r="S1" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="166"/>
+      <c r="T1" s="145"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="150"/>
-      <c r="H2" s="168"/>
-      <c r="I2" s="168"/>
-      <c r="J2" s="151"/>
-      <c r="K2" s="150"/>
-      <c r="L2" s="168"/>
-      <c r="M2" s="168"/>
-      <c r="N2" s="151"/>
-      <c r="O2" s="150"/>
-      <c r="P2" s="151"/>
-      <c r="Q2" s="150"/>
-      <c r="R2" s="151"/>
-      <c r="S2" s="150"/>
-      <c r="T2" s="169"/>
+      <c r="A2" s="109"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="139"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="139"/>
+      <c r="M2" s="139"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="117"/>
+      <c r="S2" s="116"/>
+      <c r="T2" s="146"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="143"/>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="152"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="144"/>
-      <c r="K3" s="152"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="144"/>
-      <c r="O3" s="152"/>
-      <c r="P3" s="144"/>
-      <c r="Q3" s="152"/>
-      <c r="R3" s="144"/>
-      <c r="S3" s="152"/>
-      <c r="T3" s="170"/>
+      <c r="A3" s="109"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="118"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="110"/>
+      <c r="K3" s="118"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="110"/>
+      <c r="O3" s="118"/>
+      <c r="P3" s="110"/>
+      <c r="Q3" s="118"/>
+      <c r="R3" s="110"/>
+      <c r="S3" s="118"/>
+      <c r="T3" s="147"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="145"/>
-      <c r="B4" s="146"/>
-      <c r="C4" s="146"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="153"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="147"/>
-      <c r="K4" s="153"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="146"/>
-      <c r="N4" s="147"/>
-      <c r="O4" s="153"/>
-      <c r="P4" s="147"/>
-      <c r="Q4" s="153"/>
-      <c r="R4" s="147"/>
-      <c r="S4" s="153"/>
-      <c r="T4" s="177"/>
+      <c r="A4" s="111"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="119"/>
+      <c r="P4" s="113"/>
+      <c r="Q4" s="119"/>
+      <c r="R4" s="113"/>
+      <c r="S4" s="119"/>
+      <c r="T4" s="160"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="164" t="s">
+      <c r="A5" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="165"/>
-      <c r="C5" s="165"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="165"/>
-      <c r="F5" s="149"/>
-      <c r="G5" s="137" t="s">
+      <c r="B5" s="141"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="141"/>
+      <c r="E5" s="141"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="165"/>
-      <c r="I5" s="165"/>
-      <c r="J5" s="165"/>
-      <c r="K5" s="165"/>
-      <c r="L5" s="165"/>
-      <c r="M5" s="165"/>
-      <c r="N5" s="165"/>
-      <c r="O5" s="165"/>
-      <c r="P5" s="165"/>
-      <c r="Q5" s="165"/>
-      <c r="R5" s="165"/>
-      <c r="S5" s="165"/>
-      <c r="T5" s="166"/>
+      <c r="H5" s="141"/>
+      <c r="I5" s="141"/>
+      <c r="J5" s="141"/>
+      <c r="K5" s="141"/>
+      <c r="L5" s="141"/>
+      <c r="M5" s="141"/>
+      <c r="N5" s="141"/>
+      <c r="O5" s="141"/>
+      <c r="P5" s="141"/>
+      <c r="Q5" s="141"/>
+      <c r="R5" s="141"/>
+      <c r="S5" s="141"/>
+      <c r="T5" s="145"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="144" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="101"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="121" t="s">
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="101"/>
-      <c r="I6" s="101"/>
-      <c r="J6" s="101"/>
-      <c r="K6" s="101"/>
-      <c r="L6" s="101"/>
-      <c r="M6" s="101"/>
-      <c r="N6" s="101"/>
-      <c r="O6" s="101"/>
-      <c r="P6" s="101"/>
-      <c r="Q6" s="101"/>
-      <c r="R6" s="101"/>
-      <c r="S6" s="101"/>
-      <c r="T6" s="159"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80"/>
+      <c r="T6" s="136"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="157" t="s">
+      <c r="A7" s="144" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="101"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="121" t="s">
+      <c r="B7" s="80"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="101"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="101"/>
-      <c r="K7" s="101"/>
-      <c r="L7" s="101"/>
-      <c r="M7" s="101"/>
-      <c r="N7" s="101"/>
-      <c r="O7" s="101"/>
-      <c r="P7" s="101"/>
-      <c r="Q7" s="101"/>
-      <c r="R7" s="101"/>
-      <c r="S7" s="101"/>
-      <c r="T7" s="159"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="80"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="80"/>
+      <c r="Q7" s="80"/>
+      <c r="R7" s="80"/>
+      <c r="S7" s="80"/>
+      <c r="T7" s="136"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11075,37 +11074,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="157" t="s">
+      <c r="A15" s="144" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="102"/>
-      <c r="C15" s="180" t="s">
+      <c r="B15" s="81"/>
+      <c r="C15" s="159" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="102"/>
-      <c r="E15" s="158" t="s">
+      <c r="D15" s="81"/>
+      <c r="E15" s="148" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="102"/>
-      <c r="G15" s="158" t="s">
+      <c r="F15" s="81"/>
+      <c r="G15" s="148" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="101"/>
-      <c r="I15" s="102"/>
-      <c r="J15" s="158" t="s">
+      <c r="H15" s="80"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="148" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="102"/>
-      <c r="L15" s="158" t="s">
+      <c r="K15" s="81"/>
+      <c r="L15" s="148" t="s">
         <v>46</v>
       </c>
-      <c r="M15" s="101"/>
-      <c r="N15" s="102"/>
-      <c r="O15" s="158" t="s">
+      <c r="M15" s="80"/>
+      <c r="N15" s="81"/>
+      <c r="O15" s="148" t="s">
         <v>47</v>
       </c>
-      <c r="P15" s="101"/>
-      <c r="Q15" s="102"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="81"/>
       <c r="R15" s="15" t="s">
         <v>48</v>
       </c>
@@ -11117,37 +11116,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="178">
+      <c r="A16" s="150">
         <v>1</v>
       </c>
-      <c r="B16" s="102"/>
-      <c r="C16" s="179" t="s">
+      <c r="B16" s="81"/>
+      <c r="C16" s="151" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="102"/>
-      <c r="E16" s="179" t="s">
+      <c r="D16" s="81"/>
+      <c r="E16" s="151" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="102"/>
-      <c r="G16" s="171" t="s">
+      <c r="F16" s="81"/>
+      <c r="G16" s="158" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="101"/>
-      <c r="I16" s="102"/>
-      <c r="J16" s="171" t="s">
+      <c r="H16" s="80"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="158" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="102"/>
-      <c r="L16" s="175" t="s">
+      <c r="K16" s="81"/>
+      <c r="L16" s="155" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="101"/>
-      <c r="N16" s="102"/>
-      <c r="O16" s="175" t="s">
+      <c r="M16" s="80"/>
+      <c r="N16" s="81"/>
+      <c r="O16" s="155" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="101"/>
-      <c r="Q16" s="102"/>
+      <c r="P16" s="80"/>
+      <c r="Q16" s="81"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
@@ -11159,37 +11158,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="178">
+      <c r="A17" s="150">
         <v>2</v>
       </c>
-      <c r="B17" s="102"/>
-      <c r="C17" s="179" t="s">
+      <c r="B17" s="81"/>
+      <c r="C17" s="151" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="102"/>
-      <c r="E17" s="179" t="s">
+      <c r="D17" s="81"/>
+      <c r="E17" s="151" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="102"/>
-      <c r="G17" s="171" t="s">
+      <c r="F17" s="81"/>
+      <c r="G17" s="158" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="101"/>
-      <c r="I17" s="102"/>
-      <c r="J17" s="171" t="s">
+      <c r="H17" s="80"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="158" t="s">
         <v>60</v>
       </c>
-      <c r="K17" s="102"/>
-      <c r="L17" s="175" t="s">
+      <c r="K17" s="81"/>
+      <c r="L17" s="155" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="101"/>
-      <c r="N17" s="102"/>
-      <c r="O17" s="175" t="s">
+      <c r="M17" s="80"/>
+      <c r="N17" s="81"/>
+      <c r="O17" s="155" t="s">
         <v>62</v>
       </c>
-      <c r="P17" s="101"/>
-      <c r="Q17" s="102"/>
+      <c r="P17" s="80"/>
+      <c r="Q17" s="81"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31"/>
       <c r="T17" s="32"/>
@@ -11201,23 +11200,23 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="178"/>
-      <c r="B18" s="102"/>
-      <c r="C18" s="179"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="179"/>
-      <c r="F18" s="102"/>
-      <c r="G18" s="171"/>
-      <c r="H18" s="101"/>
-      <c r="I18" s="102"/>
-      <c r="J18" s="171"/>
-      <c r="K18" s="102"/>
-      <c r="L18" s="175"/>
-      <c r="M18" s="101"/>
-      <c r="N18" s="102"/>
-      <c r="O18" s="175"/>
-      <c r="P18" s="101"/>
-      <c r="Q18" s="102"/>
+      <c r="A18" s="150"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="151"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="151"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="158"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="155"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="155"/>
+      <c r="P18" s="80"/>
+      <c r="Q18" s="81"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
       <c r="T18" s="32"/>
@@ -11229,23 +11228,23 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="178"/>
-      <c r="B19" s="102"/>
-      <c r="C19" s="179"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="179"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="171"/>
-      <c r="H19" s="101"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="171"/>
-      <c r="K19" s="102"/>
-      <c r="L19" s="175"/>
-      <c r="M19" s="101"/>
-      <c r="N19" s="102"/>
-      <c r="O19" s="175"/>
-      <c r="P19" s="101"/>
-      <c r="Q19" s="102"/>
+      <c r="A19" s="150"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="151"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="80"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="158"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="155"/>
+      <c r="M19" s="80"/>
+      <c r="N19" s="81"/>
+      <c r="O19" s="155"/>
+      <c r="P19" s="80"/>
+      <c r="Q19" s="81"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
       <c r="T19" s="32"/>
@@ -11257,23 +11256,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="178"/>
-      <c r="B20" s="102"/>
-      <c r="C20" s="179"/>
-      <c r="D20" s="102"/>
-      <c r="E20" s="179"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="171"/>
-      <c r="H20" s="101"/>
-      <c r="I20" s="102"/>
-      <c r="J20" s="171"/>
-      <c r="K20" s="102"/>
-      <c r="L20" s="175"/>
-      <c r="M20" s="101"/>
-      <c r="N20" s="102"/>
-      <c r="O20" s="175"/>
-      <c r="P20" s="101"/>
-      <c r="Q20" s="102"/>
+      <c r="A20" s="150"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="151"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="151"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="158"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="158"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="155"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="81"/>
+      <c r="O20" s="155"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="81"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -11285,23 +11284,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="178"/>
-      <c r="B21" s="102"/>
-      <c r="C21" s="179"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="179"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="171"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="171"/>
-      <c r="K21" s="102"/>
-      <c r="L21" s="175"/>
-      <c r="M21" s="101"/>
-      <c r="N21" s="102"/>
-      <c r="O21" s="175"/>
-      <c r="P21" s="101"/>
-      <c r="Q21" s="102"/>
+      <c r="A21" s="150"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="151"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="151"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="158"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="158"/>
+      <c r="K21" s="81"/>
+      <c r="L21" s="155"/>
+      <c r="M21" s="80"/>
+      <c r="N21" s="81"/>
+      <c r="O21" s="155"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="81"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -11313,23 +11312,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="178"/>
-      <c r="B22" s="102"/>
-      <c r="C22" s="179"/>
-      <c r="D22" s="102"/>
-      <c r="E22" s="179"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="171"/>
-      <c r="H22" s="101"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="171"/>
-      <c r="K22" s="102"/>
-      <c r="L22" s="175"/>
-      <c r="M22" s="101"/>
-      <c r="N22" s="102"/>
-      <c r="O22" s="175"/>
-      <c r="P22" s="101"/>
-      <c r="Q22" s="102"/>
+      <c r="A22" s="150"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="151"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="151"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="158"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="158"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="155"/>
+      <c r="M22" s="80"/>
+      <c r="N22" s="81"/>
+      <c r="O22" s="155"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="81"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -11341,23 +11340,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="178"/>
-      <c r="B23" s="102"/>
-      <c r="C23" s="179"/>
-      <c r="D23" s="102"/>
-      <c r="E23" s="179"/>
-      <c r="F23" s="102"/>
-      <c r="G23" s="171"/>
-      <c r="H23" s="101"/>
-      <c r="I23" s="102"/>
-      <c r="J23" s="171"/>
-      <c r="K23" s="102"/>
-      <c r="L23" s="175"/>
-      <c r="M23" s="101"/>
-      <c r="N23" s="102"/>
-      <c r="O23" s="175"/>
-      <c r="P23" s="101"/>
-      <c r="Q23" s="102"/>
+      <c r="A23" s="150"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="151"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="158"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="158"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="155"/>
+      <c r="M23" s="80"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="155"/>
+      <c r="P23" s="80"/>
+      <c r="Q23" s="81"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -11369,23 +11368,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="178"/>
-      <c r="B24" s="102"/>
-      <c r="C24" s="179"/>
-      <c r="D24" s="102"/>
-      <c r="E24" s="179"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="171"/>
-      <c r="H24" s="101"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="171"/>
-      <c r="K24" s="102"/>
-      <c r="L24" s="175"/>
-      <c r="M24" s="101"/>
-      <c r="N24" s="102"/>
-      <c r="O24" s="175"/>
-      <c r="P24" s="101"/>
-      <c r="Q24" s="102"/>
+      <c r="A24" s="150"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="151"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="151"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="158"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="158"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="155"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="155"/>
+      <c r="P24" s="80"/>
+      <c r="Q24" s="81"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -11397,23 +11396,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="178"/>
-      <c r="B25" s="102"/>
-      <c r="C25" s="179"/>
-      <c r="D25" s="102"/>
-      <c r="E25" s="179"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="171"/>
-      <c r="H25" s="101"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="171"/>
-      <c r="K25" s="102"/>
-      <c r="L25" s="175"/>
-      <c r="M25" s="101"/>
-      <c r="N25" s="102"/>
-      <c r="O25" s="175"/>
-      <c r="P25" s="101"/>
-      <c r="Q25" s="102"/>
+      <c r="A25" s="150"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="151"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="151"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="158"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="158"/>
+      <c r="K25" s="81"/>
+      <c r="L25" s="155"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="81"/>
+      <c r="O25" s="155"/>
+      <c r="P25" s="80"/>
+      <c r="Q25" s="81"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -11425,23 +11424,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="178"/>
-      <c r="B26" s="102"/>
-      <c r="C26" s="179"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="179"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="171"/>
-      <c r="H26" s="101"/>
-      <c r="I26" s="102"/>
-      <c r="J26" s="171"/>
-      <c r="K26" s="102"/>
-      <c r="L26" s="175"/>
-      <c r="M26" s="101"/>
-      <c r="N26" s="102"/>
-      <c r="O26" s="175"/>
-      <c r="P26" s="101"/>
-      <c r="Q26" s="102"/>
+      <c r="A26" s="150"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="151"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="151"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="158"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="158"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="155"/>
+      <c r="M26" s="80"/>
+      <c r="N26" s="81"/>
+      <c r="O26" s="155"/>
+      <c r="P26" s="80"/>
+      <c r="Q26" s="81"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -11453,23 +11452,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="178"/>
-      <c r="B27" s="102"/>
-      <c r="C27" s="179"/>
-      <c r="D27" s="102"/>
-      <c r="E27" s="179"/>
-      <c r="F27" s="102"/>
-      <c r="G27" s="171"/>
-      <c r="H27" s="101"/>
-      <c r="I27" s="102"/>
-      <c r="J27" s="171"/>
-      <c r="K27" s="102"/>
-      <c r="L27" s="175"/>
-      <c r="M27" s="101"/>
-      <c r="N27" s="102"/>
-      <c r="O27" s="175"/>
-      <c r="P27" s="101"/>
-      <c r="Q27" s="102"/>
+      <c r="A27" s="150"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="151"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="151"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="158"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="158"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="155"/>
+      <c r="M27" s="80"/>
+      <c r="N27" s="81"/>
+      <c r="O27" s="155"/>
+      <c r="P27" s="80"/>
+      <c r="Q27" s="81"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -11481,23 +11480,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="178"/>
-      <c r="B28" s="102"/>
-      <c r="C28" s="179"/>
-      <c r="D28" s="102"/>
-      <c r="E28" s="179"/>
-      <c r="F28" s="102"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="101"/>
-      <c r="I28" s="102"/>
-      <c r="J28" s="171"/>
-      <c r="K28" s="102"/>
-      <c r="L28" s="175"/>
-      <c r="M28" s="101"/>
-      <c r="N28" s="102"/>
-      <c r="O28" s="175"/>
-      <c r="P28" s="101"/>
-      <c r="Q28" s="102"/>
+      <c r="A28" s="150"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="151"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="151"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="158"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="158"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="155"/>
+      <c r="M28" s="80"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="155"/>
+      <c r="P28" s="80"/>
+      <c r="Q28" s="81"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -11509,23 +11508,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="178"/>
-      <c r="B29" s="102"/>
-      <c r="C29" s="179"/>
-      <c r="D29" s="102"/>
-      <c r="E29" s="179"/>
-      <c r="F29" s="102"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="101"/>
-      <c r="I29" s="102"/>
-      <c r="J29" s="171"/>
-      <c r="K29" s="102"/>
-      <c r="L29" s="175"/>
-      <c r="M29" s="101"/>
-      <c r="N29" s="102"/>
-      <c r="O29" s="175"/>
-      <c r="P29" s="101"/>
-      <c r="Q29" s="102"/>
+      <c r="A29" s="150"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="151"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="151"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="158"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="158"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="155"/>
+      <c r="M29" s="80"/>
+      <c r="N29" s="81"/>
+      <c r="O29" s="155"/>
+      <c r="P29" s="80"/>
+      <c r="Q29" s="81"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -11537,23 +11536,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="178"/>
-      <c r="B30" s="102"/>
-      <c r="C30" s="179"/>
-      <c r="D30" s="102"/>
-      <c r="E30" s="179"/>
-      <c r="F30" s="102"/>
-      <c r="G30" s="171"/>
-      <c r="H30" s="101"/>
-      <c r="I30" s="102"/>
-      <c r="J30" s="171"/>
-      <c r="K30" s="102"/>
-      <c r="L30" s="175"/>
-      <c r="M30" s="101"/>
-      <c r="N30" s="102"/>
-      <c r="O30" s="175"/>
-      <c r="P30" s="101"/>
-      <c r="Q30" s="102"/>
+      <c r="A30" s="150"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="151"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="151"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="158"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="158"/>
+      <c r="K30" s="81"/>
+      <c r="L30" s="155"/>
+      <c r="M30" s="80"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="155"/>
+      <c r="P30" s="80"/>
+      <c r="Q30" s="81"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -11565,23 +11564,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="181"/>
-      <c r="B31" s="174"/>
-      <c r="C31" s="182"/>
-      <c r="D31" s="174"/>
-      <c r="E31" s="182"/>
-      <c r="F31" s="174"/>
-      <c r="G31" s="172"/>
-      <c r="H31" s="173"/>
-      <c r="I31" s="174"/>
-      <c r="J31" s="172"/>
-      <c r="K31" s="174"/>
-      <c r="L31" s="176"/>
-      <c r="M31" s="173"/>
-      <c r="N31" s="174"/>
-      <c r="O31" s="176"/>
-      <c r="P31" s="173"/>
-      <c r="Q31" s="174"/>
+      <c r="A31" s="152"/>
+      <c r="B31" s="153"/>
+      <c r="C31" s="154"/>
+      <c r="D31" s="153"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="153"/>
+      <c r="G31" s="161"/>
+      <c r="H31" s="157"/>
+      <c r="I31" s="153"/>
+      <c r="J31" s="161"/>
+      <c r="K31" s="153"/>
+      <c r="L31" s="156"/>
+      <c r="M31" s="157"/>
+      <c r="N31" s="153"/>
+      <c r="O31" s="156"/>
+      <c r="P31" s="157"/>
+      <c r="Q31" s="153"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -12579,6 +12578,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -12603,118 +12714,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12739,72 +12738,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="171" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="90" t="s">
+      <c r="B1" s="171"/>
+      <c r="C1" s="172" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="91"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="93" t="s">
+      <c r="D1" s="173"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="175" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="95"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
+      <c r="L1" s="176"/>
+      <c r="M1" s="177"/>
       <c r="N1" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="O1" s="93" t="s">
+      <c r="O1" s="175" t="s">
         <v>123</v>
       </c>
-      <c r="P1" s="95"/>
+      <c r="P1" s="177"/>
       <c r="Q1" s="57" t="s">
         <v>124</v>
       </c>
-      <c r="R1" s="93" t="s">
+      <c r="R1" s="175" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="95"/>
+      <c r="S1" s="177"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="89"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="90" t="s">
+      <c r="A2" s="171"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="172" t="s">
         <v>126</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="93" t="s">
+      <c r="D2" s="173"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="175" t="s">
         <v>127</v>
       </c>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="95"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
+      <c r="L2" s="176"/>
+      <c r="M2" s="177"/>
       <c r="N2" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="O2" s="96">
+      <c r="O2" s="178">
         <v>46192</v>
       </c>
-      <c r="P2" s="97"/>
+      <c r="P2" s="179"/>
       <c r="Q2" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="R2" s="98" t="s">
+      <c r="R2" s="180" t="s">
         <v>123</v>
       </c>
-      <c r="S2" s="99"/>
+      <c r="S2" s="181"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="60"/>
@@ -12834,33 +12833,33 @@
       <c r="B4" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="80" t="s">
+      <c r="C4" s="162" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="80" t="s">
+      <c r="D4" s="163"/>
+      <c r="E4" s="163"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="164"/>
+      <c r="H4" s="162" t="s">
         <v>133</v>
       </c>
-      <c r="I4" s="81"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="81"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="80" t="s">
+      <c r="I4" s="163"/>
+      <c r="J4" s="163"/>
+      <c r="K4" s="163"/>
+      <c r="L4" s="163"/>
+      <c r="M4" s="164"/>
+      <c r="N4" s="162" t="s">
         <v>134</v>
       </c>
-      <c r="O4" s="81"/>
-      <c r="P4" s="82"/>
+      <c r="O4" s="163"/>
+      <c r="P4" s="164"/>
       <c r="Q4" s="62" t="s">
         <v>135</v>
       </c>
-      <c r="R4" s="80" t="s">
+      <c r="R4" s="162" t="s">
         <v>136</v>
       </c>
-      <c r="S4" s="82"/>
+      <c r="S4" s="164"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="64">
@@ -12869,1021 +12868,1209 @@
       <c r="B5" s="65" t="s">
         <v>137</v>
       </c>
-      <c r="C5" s="83" t="s">
+      <c r="C5" s="165" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83" t="s">
+      <c r="D5" s="165"/>
+      <c r="E5" s="165"/>
+      <c r="F5" s="165"/>
+      <c r="G5" s="165"/>
+      <c r="H5" s="165" t="s">
         <v>139</v>
       </c>
-      <c r="I5" s="83"/>
-      <c r="J5" s="83"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="84" t="s">
+      <c r="I5" s="165"/>
+      <c r="J5" s="165"/>
+      <c r="K5" s="165"/>
+      <c r="L5" s="165"/>
+      <c r="M5" s="165"/>
+      <c r="N5" s="166" t="s">
         <v>140</v>
       </c>
-      <c r="O5" s="85"/>
-      <c r="P5" s="86"/>
-      <c r="Q5" s="64" t="s">
-        <v>141</v>
-      </c>
-      <c r="R5" s="87"/>
-      <c r="S5" s="88"/>
+      <c r="O5" s="167"/>
+      <c r="P5" s="168"/>
+      <c r="Q5" s="193">
+        <v>46192</v>
+      </c>
+      <c r="R5" s="169"/>
+      <c r="S5" s="170"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="66"/>
       <c r="B6" s="66"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="78"/>
-      <c r="P6" s="79"/>
+      <c r="C6" s="182"/>
+      <c r="D6" s="182"/>
+      <c r="E6" s="182"/>
+      <c r="F6" s="182"/>
+      <c r="G6" s="182"/>
+      <c r="H6" s="182"/>
+      <c r="I6" s="182"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="182"/>
+      <c r="L6" s="182"/>
+      <c r="M6" s="182"/>
+      <c r="N6" s="187"/>
+      <c r="O6" s="188"/>
+      <c r="P6" s="189"/>
       <c r="Q6" s="67"/>
-      <c r="R6" s="76"/>
-      <c r="S6" s="76"/>
+      <c r="R6" s="186"/>
+      <c r="S6" s="186"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="66"/>
       <c r="B7" s="66"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="75"/>
+      <c r="C7" s="182"/>
+      <c r="D7" s="182"/>
+      <c r="E7" s="182"/>
+      <c r="F7" s="182"/>
+      <c r="G7" s="182"/>
+      <c r="H7" s="182"/>
+      <c r="I7" s="182"/>
+      <c r="J7" s="182"/>
+      <c r="K7" s="182"/>
+      <c r="L7" s="182"/>
+      <c r="M7" s="182"/>
+      <c r="N7" s="183"/>
+      <c r="O7" s="184"/>
+      <c r="P7" s="185"/>
       <c r="Q7" s="67"/>
-      <c r="R7" s="76"/>
-      <c r="S7" s="76"/>
+      <c r="R7" s="186"/>
+      <c r="S7" s="186"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="66"/>
       <c r="B8" s="66"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="73"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="75"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="182"/>
+      <c r="E8" s="182"/>
+      <c r="F8" s="182"/>
+      <c r="G8" s="182"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="182"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="182"/>
+      <c r="M8" s="182"/>
+      <c r="N8" s="183"/>
+      <c r="O8" s="184"/>
+      <c r="P8" s="185"/>
       <c r="Q8" s="67"/>
-      <c r="R8" s="76"/>
-      <c r="S8" s="76"/>
+      <c r="R8" s="186"/>
+      <c r="S8" s="186"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="66"/>
       <c r="B9" s="66"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="73"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="75"/>
+      <c r="C9" s="182"/>
+      <c r="D9" s="182"/>
+      <c r="E9" s="182"/>
+      <c r="F9" s="182"/>
+      <c r="G9" s="182"/>
+      <c r="H9" s="182"/>
+      <c r="I9" s="182"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="182"/>
+      <c r="M9" s="182"/>
+      <c r="N9" s="183"/>
+      <c r="O9" s="184"/>
+      <c r="P9" s="185"/>
       <c r="Q9" s="66"/>
-      <c r="R9" s="76"/>
-      <c r="S9" s="76"/>
+      <c r="R9" s="186"/>
+      <c r="S9" s="186"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="66"/>
       <c r="B10" s="66"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="71"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="73"/>
-      <c r="O10" s="74"/>
-      <c r="P10" s="75"/>
+      <c r="C10" s="182"/>
+      <c r="D10" s="182"/>
+      <c r="E10" s="182"/>
+      <c r="F10" s="182"/>
+      <c r="G10" s="182"/>
+      <c r="H10" s="190"/>
+      <c r="I10" s="191"/>
+      <c r="J10" s="191"/>
+      <c r="K10" s="191"/>
+      <c r="L10" s="191"/>
+      <c r="M10" s="192"/>
+      <c r="N10" s="183"/>
+      <c r="O10" s="184"/>
+      <c r="P10" s="185"/>
       <c r="Q10" s="67"/>
-      <c r="R10" s="76"/>
-      <c r="S10" s="76"/>
+      <c r="R10" s="186"/>
+      <c r="S10" s="186"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="66"/>
       <c r="B11" s="66"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="73"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="75"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="190"/>
+      <c r="I11" s="191"/>
+      <c r="J11" s="191"/>
+      <c r="K11" s="191"/>
+      <c r="L11" s="191"/>
+      <c r="M11" s="192"/>
+      <c r="N11" s="183"/>
+      <c r="O11" s="184"/>
+      <c r="P11" s="185"/>
       <c r="Q11" s="66"/>
-      <c r="R11" s="76"/>
-      <c r="S11" s="76"/>
+      <c r="R11" s="186"/>
+      <c r="S11" s="186"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="66"/>
       <c r="B12" s="66"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="73"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="75"/>
+      <c r="C12" s="182"/>
+      <c r="D12" s="182"/>
+      <c r="E12" s="182"/>
+      <c r="F12" s="182"/>
+      <c r="G12" s="182"/>
+      <c r="H12" s="190"/>
+      <c r="I12" s="191"/>
+      <c r="J12" s="191"/>
+      <c r="K12" s="191"/>
+      <c r="L12" s="191"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="183"/>
+      <c r="O12" s="184"/>
+      <c r="P12" s="185"/>
       <c r="Q12" s="66"/>
-      <c r="R12" s="76"/>
-      <c r="S12" s="76"/>
+      <c r="R12" s="186"/>
+      <c r="S12" s="186"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="66"/>
       <c r="B13" s="66"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="71"/>
-      <c r="M13" s="72"/>
-      <c r="N13" s="73"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="75"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="182"/>
+      <c r="E13" s="182"/>
+      <c r="F13" s="182"/>
+      <c r="G13" s="182"/>
+      <c r="H13" s="190"/>
+      <c r="I13" s="191"/>
+      <c r="J13" s="191"/>
+      <c r="K13" s="191"/>
+      <c r="L13" s="191"/>
+      <c r="M13" s="192"/>
+      <c r="N13" s="183"/>
+      <c r="O13" s="184"/>
+      <c r="P13" s="185"/>
       <c r="Q13" s="66"/>
-      <c r="R13" s="76"/>
-      <c r="S13" s="76"/>
+      <c r="R13" s="186"/>
+      <c r="S13" s="186"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="66"/>
       <c r="B14" s="66"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="71"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="73"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="75"/>
+      <c r="C14" s="182"/>
+      <c r="D14" s="182"/>
+      <c r="E14" s="182"/>
+      <c r="F14" s="182"/>
+      <c r="G14" s="182"/>
+      <c r="H14" s="190"/>
+      <c r="I14" s="191"/>
+      <c r="J14" s="191"/>
+      <c r="K14" s="191"/>
+      <c r="L14" s="191"/>
+      <c r="M14" s="192"/>
+      <c r="N14" s="183"/>
+      <c r="O14" s="184"/>
+      <c r="P14" s="185"/>
       <c r="Q14" s="66"/>
-      <c r="R14" s="76"/>
-      <c r="S14" s="76"/>
+      <c r="R14" s="186"/>
+      <c r="S14" s="186"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="66"/>
       <c r="B15" s="66"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="73"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="75"/>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
+      <c r="E15" s="182"/>
+      <c r="F15" s="182"/>
+      <c r="G15" s="182"/>
+      <c r="H15" s="190"/>
+      <c r="I15" s="191"/>
+      <c r="J15" s="191"/>
+      <c r="K15" s="191"/>
+      <c r="L15" s="191"/>
+      <c r="M15" s="192"/>
+      <c r="N15" s="183"/>
+      <c r="O15" s="184"/>
+      <c r="P15" s="185"/>
       <c r="Q15" s="66"/>
-      <c r="R15" s="76"/>
-      <c r="S15" s="76"/>
+      <c r="R15" s="186"/>
+      <c r="S15" s="186"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="66"/>
       <c r="B16" s="66"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="73"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="75"/>
+      <c r="C16" s="182"/>
+      <c r="D16" s="182"/>
+      <c r="E16" s="182"/>
+      <c r="F16" s="182"/>
+      <c r="G16" s="182"/>
+      <c r="H16" s="190"/>
+      <c r="I16" s="191"/>
+      <c r="J16" s="191"/>
+      <c r="K16" s="191"/>
+      <c r="L16" s="191"/>
+      <c r="M16" s="192"/>
+      <c r="N16" s="183"/>
+      <c r="O16" s="184"/>
+      <c r="P16" s="185"/>
       <c r="Q16" s="66"/>
-      <c r="R16" s="76"/>
-      <c r="S16" s="76"/>
+      <c r="R16" s="186"/>
+      <c r="S16" s="186"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="66"/>
       <c r="B17" s="66"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="73"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="75"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="182"/>
+      <c r="E17" s="182"/>
+      <c r="F17" s="182"/>
+      <c r="G17" s="182"/>
+      <c r="H17" s="190"/>
+      <c r="I17" s="191"/>
+      <c r="J17" s="191"/>
+      <c r="K17" s="191"/>
+      <c r="L17" s="191"/>
+      <c r="M17" s="192"/>
+      <c r="N17" s="183"/>
+      <c r="O17" s="184"/>
+      <c r="P17" s="185"/>
       <c r="Q17" s="66"/>
-      <c r="R17" s="76"/>
-      <c r="S17" s="76"/>
+      <c r="R17" s="186"/>
+      <c r="S17" s="186"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="66"/>
       <c r="B18" s="66"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="71"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="73"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="75"/>
+      <c r="C18" s="182"/>
+      <c r="D18" s="182"/>
+      <c r="E18" s="182"/>
+      <c r="F18" s="182"/>
+      <c r="G18" s="182"/>
+      <c r="H18" s="190"/>
+      <c r="I18" s="191"/>
+      <c r="J18" s="191"/>
+      <c r="K18" s="191"/>
+      <c r="L18" s="191"/>
+      <c r="M18" s="192"/>
+      <c r="N18" s="183"/>
+      <c r="O18" s="184"/>
+      <c r="P18" s="185"/>
       <c r="Q18" s="66"/>
-      <c r="R18" s="76"/>
-      <c r="S18" s="76"/>
+      <c r="R18" s="186"/>
+      <c r="S18" s="186"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="66"/>
       <c r="B19" s="66"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="73"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="75"/>
+      <c r="C19" s="182"/>
+      <c r="D19" s="182"/>
+      <c r="E19" s="182"/>
+      <c r="F19" s="182"/>
+      <c r="G19" s="182"/>
+      <c r="H19" s="190"/>
+      <c r="I19" s="191"/>
+      <c r="J19" s="191"/>
+      <c r="K19" s="191"/>
+      <c r="L19" s="191"/>
+      <c r="M19" s="192"/>
+      <c r="N19" s="183"/>
+      <c r="O19" s="184"/>
+      <c r="P19" s="185"/>
       <c r="Q19" s="66"/>
-      <c r="R19" s="76"/>
-      <c r="S19" s="76"/>
+      <c r="R19" s="186"/>
+      <c r="S19" s="186"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="66"/>
       <c r="B20" s="66"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="71"/>
-      <c r="M20" s="72"/>
-      <c r="N20" s="73"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="75"/>
+      <c r="C20" s="182"/>
+      <c r="D20" s="182"/>
+      <c r="E20" s="182"/>
+      <c r="F20" s="182"/>
+      <c r="G20" s="182"/>
+      <c r="H20" s="190"/>
+      <c r="I20" s="191"/>
+      <c r="J20" s="191"/>
+      <c r="K20" s="191"/>
+      <c r="L20" s="191"/>
+      <c r="M20" s="192"/>
+      <c r="N20" s="183"/>
+      <c r="O20" s="184"/>
+      <c r="P20" s="185"/>
       <c r="Q20" s="66"/>
-      <c r="R20" s="76"/>
-      <c r="S20" s="76"/>
+      <c r="R20" s="186"/>
+      <c r="S20" s="186"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="66"/>
       <c r="B21" s="66"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="71"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="73"/>
-      <c r="O21" s="74"/>
-      <c r="P21" s="75"/>
+      <c r="C21" s="182"/>
+      <c r="D21" s="182"/>
+      <c r="E21" s="182"/>
+      <c r="F21" s="182"/>
+      <c r="G21" s="182"/>
+      <c r="H21" s="190"/>
+      <c r="I21" s="191"/>
+      <c r="J21" s="191"/>
+      <c r="K21" s="191"/>
+      <c r="L21" s="191"/>
+      <c r="M21" s="192"/>
+      <c r="N21" s="183"/>
+      <c r="O21" s="184"/>
+      <c r="P21" s="185"/>
       <c r="Q21" s="66"/>
-      <c r="R21" s="76"/>
-      <c r="S21" s="76"/>
+      <c r="R21" s="186"/>
+      <c r="S21" s="186"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="66"/>
       <c r="B22" s="66"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="73"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="75"/>
+      <c r="C22" s="182"/>
+      <c r="D22" s="182"/>
+      <c r="E22" s="182"/>
+      <c r="F22" s="182"/>
+      <c r="G22" s="182"/>
+      <c r="H22" s="190"/>
+      <c r="I22" s="191"/>
+      <c r="J22" s="191"/>
+      <c r="K22" s="191"/>
+      <c r="L22" s="191"/>
+      <c r="M22" s="192"/>
+      <c r="N22" s="183"/>
+      <c r="O22" s="184"/>
+      <c r="P22" s="185"/>
       <c r="Q22" s="66"/>
-      <c r="R22" s="76"/>
-      <c r="S22" s="76"/>
+      <c r="R22" s="186"/>
+      <c r="S22" s="186"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="66"/>
       <c r="B23" s="66"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="71"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="73"/>
-      <c r="O23" s="74"/>
-      <c r="P23" s="75"/>
+      <c r="C23" s="182"/>
+      <c r="D23" s="182"/>
+      <c r="E23" s="182"/>
+      <c r="F23" s="182"/>
+      <c r="G23" s="182"/>
+      <c r="H23" s="190"/>
+      <c r="I23" s="191"/>
+      <c r="J23" s="191"/>
+      <c r="K23" s="191"/>
+      <c r="L23" s="191"/>
+      <c r="M23" s="192"/>
+      <c r="N23" s="183"/>
+      <c r="O23" s="184"/>
+      <c r="P23" s="185"/>
       <c r="Q23" s="66"/>
-      <c r="R23" s="76"/>
-      <c r="S23" s="76"/>
+      <c r="R23" s="186"/>
+      <c r="S23" s="186"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="66"/>
       <c r="B24" s="66"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="71"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="73"/>
-      <c r="O24" s="74"/>
-      <c r="P24" s="75"/>
+      <c r="C24" s="182"/>
+      <c r="D24" s="182"/>
+      <c r="E24" s="182"/>
+      <c r="F24" s="182"/>
+      <c r="G24" s="182"/>
+      <c r="H24" s="190"/>
+      <c r="I24" s="191"/>
+      <c r="J24" s="191"/>
+      <c r="K24" s="191"/>
+      <c r="L24" s="191"/>
+      <c r="M24" s="192"/>
+      <c r="N24" s="183"/>
+      <c r="O24" s="184"/>
+      <c r="P24" s="185"/>
       <c r="Q24" s="66"/>
-      <c r="R24" s="76"/>
-      <c r="S24" s="76"/>
+      <c r="R24" s="186"/>
+      <c r="S24" s="186"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="71"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="73"/>
-      <c r="O25" s="74"/>
-      <c r="P25" s="75"/>
+      <c r="C25" s="182"/>
+      <c r="D25" s="182"/>
+      <c r="E25" s="182"/>
+      <c r="F25" s="182"/>
+      <c r="G25" s="182"/>
+      <c r="H25" s="190"/>
+      <c r="I25" s="191"/>
+      <c r="J25" s="191"/>
+      <c r="K25" s="191"/>
+      <c r="L25" s="191"/>
+      <c r="M25" s="192"/>
+      <c r="N25" s="183"/>
+      <c r="O25" s="184"/>
+      <c r="P25" s="185"/>
       <c r="Q25" s="66"/>
-      <c r="R25" s="76"/>
-      <c r="S25" s="76"/>
+      <c r="R25" s="186"/>
+      <c r="S25" s="186"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="66"/>
       <c r="B26" s="66"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="71"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="73"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="75"/>
+      <c r="C26" s="182"/>
+      <c r="D26" s="182"/>
+      <c r="E26" s="182"/>
+      <c r="F26" s="182"/>
+      <c r="G26" s="182"/>
+      <c r="H26" s="190"/>
+      <c r="I26" s="191"/>
+      <c r="J26" s="191"/>
+      <c r="K26" s="191"/>
+      <c r="L26" s="191"/>
+      <c r="M26" s="192"/>
+      <c r="N26" s="183"/>
+      <c r="O26" s="184"/>
+      <c r="P26" s="185"/>
       <c r="Q26" s="66"/>
-      <c r="R26" s="76"/>
-      <c r="S26" s="76"/>
+      <c r="R26" s="186"/>
+      <c r="S26" s="186"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="66"/>
       <c r="B27" s="66"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="72"/>
-      <c r="N27" s="73"/>
-      <c r="O27" s="74"/>
-      <c r="P27" s="75"/>
+      <c r="C27" s="182"/>
+      <c r="D27" s="182"/>
+      <c r="E27" s="182"/>
+      <c r="F27" s="182"/>
+      <c r="G27" s="182"/>
+      <c r="H27" s="190"/>
+      <c r="I27" s="191"/>
+      <c r="J27" s="191"/>
+      <c r="K27" s="191"/>
+      <c r="L27" s="191"/>
+      <c r="M27" s="192"/>
+      <c r="N27" s="183"/>
+      <c r="O27" s="184"/>
+      <c r="P27" s="185"/>
       <c r="Q27" s="66"/>
-      <c r="R27" s="76"/>
-      <c r="S27" s="76"/>
+      <c r="R27" s="186"/>
+      <c r="S27" s="186"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="66"/>
       <c r="B28" s="66"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="71"/>
-      <c r="L28" s="71"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="73"/>
-      <c r="O28" s="74"/>
-      <c r="P28" s="75"/>
+      <c r="C28" s="182"/>
+      <c r="D28" s="182"/>
+      <c r="E28" s="182"/>
+      <c r="F28" s="182"/>
+      <c r="G28" s="182"/>
+      <c r="H28" s="190"/>
+      <c r="I28" s="191"/>
+      <c r="J28" s="191"/>
+      <c r="K28" s="191"/>
+      <c r="L28" s="191"/>
+      <c r="M28" s="192"/>
+      <c r="N28" s="183"/>
+      <c r="O28" s="184"/>
+      <c r="P28" s="185"/>
       <c r="Q28" s="66"/>
-      <c r="R28" s="76"/>
-      <c r="S28" s="76"/>
+      <c r="R28" s="186"/>
+      <c r="S28" s="186"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="66"/>
       <c r="B29" s="66"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="69"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="71"/>
-      <c r="L29" s="71"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="73"/>
-      <c r="O29" s="74"/>
-      <c r="P29" s="75"/>
+      <c r="C29" s="182"/>
+      <c r="D29" s="182"/>
+      <c r="E29" s="182"/>
+      <c r="F29" s="182"/>
+      <c r="G29" s="182"/>
+      <c r="H29" s="190"/>
+      <c r="I29" s="191"/>
+      <c r="J29" s="191"/>
+      <c r="K29" s="191"/>
+      <c r="L29" s="191"/>
+      <c r="M29" s="192"/>
+      <c r="N29" s="183"/>
+      <c r="O29" s="184"/>
+      <c r="P29" s="185"/>
       <c r="Q29" s="66"/>
-      <c r="R29" s="76"/>
-      <c r="S29" s="76"/>
+      <c r="R29" s="186"/>
+      <c r="S29" s="186"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="66"/>
       <c r="B30" s="66"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="71"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="73"/>
-      <c r="O30" s="74"/>
-      <c r="P30" s="75"/>
+      <c r="C30" s="182"/>
+      <c r="D30" s="182"/>
+      <c r="E30" s="182"/>
+      <c r="F30" s="182"/>
+      <c r="G30" s="182"/>
+      <c r="H30" s="190"/>
+      <c r="I30" s="191"/>
+      <c r="J30" s="191"/>
+      <c r="K30" s="191"/>
+      <c r="L30" s="191"/>
+      <c r="M30" s="192"/>
+      <c r="N30" s="183"/>
+      <c r="O30" s="184"/>
+      <c r="P30" s="185"/>
       <c r="Q30" s="66"/>
-      <c r="R30" s="76"/>
-      <c r="S30" s="76"/>
+      <c r="R30" s="186"/>
+      <c r="S30" s="186"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="66"/>
       <c r="B31" s="66"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="73"/>
-      <c r="O31" s="74"/>
-      <c r="P31" s="75"/>
+      <c r="C31" s="182"/>
+      <c r="D31" s="182"/>
+      <c r="E31" s="182"/>
+      <c r="F31" s="182"/>
+      <c r="G31" s="182"/>
+      <c r="H31" s="190"/>
+      <c r="I31" s="191"/>
+      <c r="J31" s="191"/>
+      <c r="K31" s="191"/>
+      <c r="L31" s="191"/>
+      <c r="M31" s="192"/>
+      <c r="N31" s="183"/>
+      <c r="O31" s="184"/>
+      <c r="P31" s="185"/>
       <c r="Q31" s="66"/>
-      <c r="R31" s="76"/>
-      <c r="S31" s="76"/>
+      <c r="R31" s="186"/>
+      <c r="S31" s="186"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="66"/>
       <c r="B32" s="66"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="71"/>
-      <c r="M32" s="72"/>
-      <c r="N32" s="73"/>
-      <c r="O32" s="74"/>
-      <c r="P32" s="75"/>
+      <c r="C32" s="182"/>
+      <c r="D32" s="182"/>
+      <c r="E32" s="182"/>
+      <c r="F32" s="182"/>
+      <c r="G32" s="182"/>
+      <c r="H32" s="190"/>
+      <c r="I32" s="191"/>
+      <c r="J32" s="191"/>
+      <c r="K32" s="191"/>
+      <c r="L32" s="191"/>
+      <c r="M32" s="192"/>
+      <c r="N32" s="183"/>
+      <c r="O32" s="184"/>
+      <c r="P32" s="185"/>
       <c r="Q32" s="66"/>
-      <c r="R32" s="76"/>
-      <c r="S32" s="76"/>
+      <c r="R32" s="186"/>
+      <c r="S32" s="186"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="66"/>
       <c r="B33" s="66"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="71"/>
-      <c r="L33" s="71"/>
-      <c r="M33" s="72"/>
-      <c r="N33" s="73"/>
-      <c r="O33" s="74"/>
-      <c r="P33" s="75"/>
+      <c r="C33" s="182"/>
+      <c r="D33" s="182"/>
+      <c r="E33" s="182"/>
+      <c r="F33" s="182"/>
+      <c r="G33" s="182"/>
+      <c r="H33" s="190"/>
+      <c r="I33" s="191"/>
+      <c r="J33" s="191"/>
+      <c r="K33" s="191"/>
+      <c r="L33" s="191"/>
+      <c r="M33" s="192"/>
+      <c r="N33" s="183"/>
+      <c r="O33" s="184"/>
+      <c r="P33" s="185"/>
       <c r="Q33" s="66"/>
-      <c r="R33" s="76"/>
-      <c r="S33" s="76"/>
+      <c r="R33" s="186"/>
+      <c r="S33" s="186"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="66"/>
       <c r="B34" s="66"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="71"/>
-      <c r="M34" s="72"/>
-      <c r="N34" s="73"/>
-      <c r="O34" s="74"/>
-      <c r="P34" s="75"/>
+      <c r="C34" s="182"/>
+      <c r="D34" s="182"/>
+      <c r="E34" s="182"/>
+      <c r="F34" s="182"/>
+      <c r="G34" s="182"/>
+      <c r="H34" s="190"/>
+      <c r="I34" s="191"/>
+      <c r="J34" s="191"/>
+      <c r="K34" s="191"/>
+      <c r="L34" s="191"/>
+      <c r="M34" s="192"/>
+      <c r="N34" s="183"/>
+      <c r="O34" s="184"/>
+      <c r="P34" s="185"/>
       <c r="Q34" s="66"/>
-      <c r="R34" s="76"/>
-      <c r="S34" s="76"/>
+      <c r="R34" s="186"/>
+      <c r="S34" s="186"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="66"/>
       <c r="B35" s="66"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="71"/>
-      <c r="M35" s="72"/>
-      <c r="N35" s="73"/>
-      <c r="O35" s="74"/>
-      <c r="P35" s="75"/>
+      <c r="C35" s="182"/>
+      <c r="D35" s="182"/>
+      <c r="E35" s="182"/>
+      <c r="F35" s="182"/>
+      <c r="G35" s="182"/>
+      <c r="H35" s="190"/>
+      <c r="I35" s="191"/>
+      <c r="J35" s="191"/>
+      <c r="K35" s="191"/>
+      <c r="L35" s="191"/>
+      <c r="M35" s="192"/>
+      <c r="N35" s="183"/>
+      <c r="O35" s="184"/>
+      <c r="P35" s="185"/>
       <c r="Q35" s="66"/>
-      <c r="R35" s="76"/>
-      <c r="S35" s="76"/>
+      <c r="R35" s="186"/>
+      <c r="S35" s="186"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="66"/>
       <c r="B36" s="66"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="71"/>
-      <c r="L36" s="71"/>
-      <c r="M36" s="72"/>
-      <c r="N36" s="73"/>
-      <c r="O36" s="74"/>
-      <c r="P36" s="75"/>
+      <c r="C36" s="182"/>
+      <c r="D36" s="182"/>
+      <c r="E36" s="182"/>
+      <c r="F36" s="182"/>
+      <c r="G36" s="182"/>
+      <c r="H36" s="190"/>
+      <c r="I36" s="191"/>
+      <c r="J36" s="191"/>
+      <c r="K36" s="191"/>
+      <c r="L36" s="191"/>
+      <c r="M36" s="192"/>
+      <c r="N36" s="183"/>
+      <c r="O36" s="184"/>
+      <c r="P36" s="185"/>
       <c r="Q36" s="66"/>
-      <c r="R36" s="76"/>
-      <c r="S36" s="76"/>
+      <c r="R36" s="186"/>
+      <c r="S36" s="186"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="66"/>
       <c r="B37" s="66"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="71"/>
-      <c r="K37" s="71"/>
-      <c r="L37" s="71"/>
-      <c r="M37" s="72"/>
-      <c r="N37" s="73"/>
-      <c r="O37" s="74"/>
-      <c r="P37" s="75"/>
+      <c r="C37" s="182"/>
+      <c r="D37" s="182"/>
+      <c r="E37" s="182"/>
+      <c r="F37" s="182"/>
+      <c r="G37" s="182"/>
+      <c r="H37" s="190"/>
+      <c r="I37" s="191"/>
+      <c r="J37" s="191"/>
+      <c r="K37" s="191"/>
+      <c r="L37" s="191"/>
+      <c r="M37" s="192"/>
+      <c r="N37" s="183"/>
+      <c r="O37" s="184"/>
+      <c r="P37" s="185"/>
       <c r="Q37" s="66"/>
-      <c r="R37" s="76"/>
-      <c r="S37" s="76"/>
+      <c r="R37" s="186"/>
+      <c r="S37" s="186"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="66"/>
       <c r="B38" s="66"/>
-      <c r="C38" s="69"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="69"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="71"/>
-      <c r="K38" s="71"/>
-      <c r="L38" s="71"/>
-      <c r="M38" s="72"/>
-      <c r="N38" s="73"/>
-      <c r="O38" s="74"/>
-      <c r="P38" s="75"/>
+      <c r="C38" s="182"/>
+      <c r="D38" s="182"/>
+      <c r="E38" s="182"/>
+      <c r="F38" s="182"/>
+      <c r="G38" s="182"/>
+      <c r="H38" s="190"/>
+      <c r="I38" s="191"/>
+      <c r="J38" s="191"/>
+      <c r="K38" s="191"/>
+      <c r="L38" s="191"/>
+      <c r="M38" s="192"/>
+      <c r="N38" s="183"/>
+      <c r="O38" s="184"/>
+      <c r="P38" s="185"/>
       <c r="Q38" s="66"/>
-      <c r="R38" s="76"/>
-      <c r="S38" s="76"/>
+      <c r="R38" s="186"/>
+      <c r="S38" s="186"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="66"/>
       <c r="B39" s="66"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="71"/>
-      <c r="L39" s="71"/>
-      <c r="M39" s="72"/>
-      <c r="N39" s="73"/>
-      <c r="O39" s="74"/>
-      <c r="P39" s="75"/>
+      <c r="C39" s="182"/>
+      <c r="D39" s="182"/>
+      <c r="E39" s="182"/>
+      <c r="F39" s="182"/>
+      <c r="G39" s="182"/>
+      <c r="H39" s="190"/>
+      <c r="I39" s="191"/>
+      <c r="J39" s="191"/>
+      <c r="K39" s="191"/>
+      <c r="L39" s="191"/>
+      <c r="M39" s="192"/>
+      <c r="N39" s="183"/>
+      <c r="O39" s="184"/>
+      <c r="P39" s="185"/>
       <c r="Q39" s="66"/>
-      <c r="R39" s="76"/>
-      <c r="S39" s="76"/>
+      <c r="R39" s="186"/>
+      <c r="S39" s="186"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="66"/>
       <c r="B40" s="66"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="69"/>
-      <c r="E40" s="69"/>
-      <c r="F40" s="69"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="70"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="71"/>
-      <c r="K40" s="71"/>
-      <c r="L40" s="71"/>
-      <c r="M40" s="72"/>
-      <c r="N40" s="73"/>
-      <c r="O40" s="74"/>
-      <c r="P40" s="75"/>
+      <c r="C40" s="182"/>
+      <c r="D40" s="182"/>
+      <c r="E40" s="182"/>
+      <c r="F40" s="182"/>
+      <c r="G40" s="182"/>
+      <c r="H40" s="190"/>
+      <c r="I40" s="191"/>
+      <c r="J40" s="191"/>
+      <c r="K40" s="191"/>
+      <c r="L40" s="191"/>
+      <c r="M40" s="192"/>
+      <c r="N40" s="183"/>
+      <c r="O40" s="184"/>
+      <c r="P40" s="185"/>
       <c r="Q40" s="66"/>
-      <c r="R40" s="76"/>
-      <c r="S40" s="76"/>
+      <c r="R40" s="186"/>
+      <c r="S40" s="186"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="66"/>
       <c r="B41" s="66"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="71"/>
-      <c r="K41" s="71"/>
-      <c r="L41" s="71"/>
-      <c r="M41" s="72"/>
-      <c r="N41" s="73"/>
-      <c r="O41" s="74"/>
-      <c r="P41" s="75"/>
+      <c r="C41" s="182"/>
+      <c r="D41" s="182"/>
+      <c r="E41" s="182"/>
+      <c r="F41" s="182"/>
+      <c r="G41" s="182"/>
+      <c r="H41" s="190"/>
+      <c r="I41" s="191"/>
+      <c r="J41" s="191"/>
+      <c r="K41" s="191"/>
+      <c r="L41" s="191"/>
+      <c r="M41" s="192"/>
+      <c r="N41" s="183"/>
+      <c r="O41" s="184"/>
+      <c r="P41" s="185"/>
       <c r="Q41" s="66"/>
-      <c r="R41" s="76"/>
-      <c r="S41" s="76"/>
+      <c r="R41" s="186"/>
+      <c r="S41" s="186"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="66"/>
       <c r="B42" s="66"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="69"/>
-      <c r="H42" s="70"/>
-      <c r="I42" s="71"/>
-      <c r="J42" s="71"/>
-      <c r="K42" s="71"/>
-      <c r="L42" s="71"/>
-      <c r="M42" s="72"/>
-      <c r="N42" s="73"/>
-      <c r="O42" s="74"/>
-      <c r="P42" s="75"/>
+      <c r="C42" s="182"/>
+      <c r="D42" s="182"/>
+      <c r="E42" s="182"/>
+      <c r="F42" s="182"/>
+      <c r="G42" s="182"/>
+      <c r="H42" s="190"/>
+      <c r="I42" s="191"/>
+      <c r="J42" s="191"/>
+      <c r="K42" s="191"/>
+      <c r="L42" s="191"/>
+      <c r="M42" s="192"/>
+      <c r="N42" s="183"/>
+      <c r="O42" s="184"/>
+      <c r="P42" s="185"/>
       <c r="Q42" s="66"/>
-      <c r="R42" s="76"/>
-      <c r="S42" s="76"/>
+      <c r="R42" s="186"/>
+      <c r="S42" s="186"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="66"/>
       <c r="B43" s="66"/>
-      <c r="C43" s="69"/>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
-      <c r="F43" s="69"/>
-      <c r="G43" s="69"/>
-      <c r="H43" s="70"/>
-      <c r="I43" s="71"/>
-      <c r="J43" s="71"/>
-      <c r="K43" s="71"/>
-      <c r="L43" s="71"/>
-      <c r="M43" s="72"/>
-      <c r="N43" s="73"/>
-      <c r="O43" s="74"/>
-      <c r="P43" s="75"/>
+      <c r="C43" s="182"/>
+      <c r="D43" s="182"/>
+      <c r="E43" s="182"/>
+      <c r="F43" s="182"/>
+      <c r="G43" s="182"/>
+      <c r="H43" s="190"/>
+      <c r="I43" s="191"/>
+      <c r="J43" s="191"/>
+      <c r="K43" s="191"/>
+      <c r="L43" s="191"/>
+      <c r="M43" s="192"/>
+      <c r="N43" s="183"/>
+      <c r="O43" s="184"/>
+      <c r="P43" s="185"/>
       <c r="Q43" s="66"/>
-      <c r="R43" s="76"/>
-      <c r="S43" s="76"/>
+      <c r="R43" s="186"/>
+      <c r="S43" s="186"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="66"/>
       <c r="B44" s="66"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="70"/>
-      <c r="I44" s="71"/>
-      <c r="J44" s="71"/>
-      <c r="K44" s="71"/>
-      <c r="L44" s="71"/>
-      <c r="M44" s="72"/>
-      <c r="N44" s="73"/>
-      <c r="O44" s="74"/>
-      <c r="P44" s="75"/>
+      <c r="C44" s="182"/>
+      <c r="D44" s="182"/>
+      <c r="E44" s="182"/>
+      <c r="F44" s="182"/>
+      <c r="G44" s="182"/>
+      <c r="H44" s="190"/>
+      <c r="I44" s="191"/>
+      <c r="J44" s="191"/>
+      <c r="K44" s="191"/>
+      <c r="L44" s="191"/>
+      <c r="M44" s="192"/>
+      <c r="N44" s="183"/>
+      <c r="O44" s="184"/>
+      <c r="P44" s="185"/>
       <c r="Q44" s="66"/>
-      <c r="R44" s="76"/>
-      <c r="S44" s="76"/>
+      <c r="R44" s="186"/>
+      <c r="S44" s="186"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="66"/>
       <c r="B45" s="66"/>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="69"/>
-      <c r="H45" s="70"/>
-      <c r="I45" s="71"/>
-      <c r="J45" s="71"/>
-      <c r="K45" s="71"/>
-      <c r="L45" s="71"/>
-      <c r="M45" s="72"/>
-      <c r="N45" s="73"/>
-      <c r="O45" s="74"/>
-      <c r="P45" s="75"/>
+      <c r="C45" s="182"/>
+      <c r="D45" s="182"/>
+      <c r="E45" s="182"/>
+      <c r="F45" s="182"/>
+      <c r="G45" s="182"/>
+      <c r="H45" s="190"/>
+      <c r="I45" s="191"/>
+      <c r="J45" s="191"/>
+      <c r="K45" s="191"/>
+      <c r="L45" s="191"/>
+      <c r="M45" s="192"/>
+      <c r="N45" s="183"/>
+      <c r="O45" s="184"/>
+      <c r="P45" s="185"/>
       <c r="Q45" s="66"/>
-      <c r="R45" s="76"/>
-      <c r="S45" s="76"/>
+      <c r="R45" s="186"/>
+      <c r="S45" s="186"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="66"/>
       <c r="B46" s="66"/>
-      <c r="C46" s="69"/>
-      <c r="D46" s="69"/>
-      <c r="E46" s="69"/>
-      <c r="F46" s="69"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="70"/>
-      <c r="I46" s="71"/>
-      <c r="J46" s="71"/>
-      <c r="K46" s="71"/>
-      <c r="L46" s="71"/>
-      <c r="M46" s="72"/>
-      <c r="N46" s="73"/>
-      <c r="O46" s="74"/>
-      <c r="P46" s="75"/>
+      <c r="C46" s="182"/>
+      <c r="D46" s="182"/>
+      <c r="E46" s="182"/>
+      <c r="F46" s="182"/>
+      <c r="G46" s="182"/>
+      <c r="H46" s="190"/>
+      <c r="I46" s="191"/>
+      <c r="J46" s="191"/>
+      <c r="K46" s="191"/>
+      <c r="L46" s="191"/>
+      <c r="M46" s="192"/>
+      <c r="N46" s="183"/>
+      <c r="O46" s="184"/>
+      <c r="P46" s="185"/>
       <c r="Q46" s="66"/>
-      <c r="R46" s="76"/>
-      <c r="S46" s="76"/>
+      <c r="R46" s="186"/>
+      <c r="S46" s="186"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="66"/>
       <c r="B47" s="66"/>
-      <c r="C47" s="69"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="71"/>
-      <c r="J47" s="71"/>
-      <c r="K47" s="71"/>
-      <c r="L47" s="71"/>
-      <c r="M47" s="72"/>
-      <c r="N47" s="73"/>
-      <c r="O47" s="74"/>
-      <c r="P47" s="75"/>
+      <c r="C47" s="182"/>
+      <c r="D47" s="182"/>
+      <c r="E47" s="182"/>
+      <c r="F47" s="182"/>
+      <c r="G47" s="182"/>
+      <c r="H47" s="190"/>
+      <c r="I47" s="191"/>
+      <c r="J47" s="191"/>
+      <c r="K47" s="191"/>
+      <c r="L47" s="191"/>
+      <c r="M47" s="192"/>
+      <c r="N47" s="183"/>
+      <c r="O47" s="184"/>
+      <c r="P47" s="185"/>
       <c r="Q47" s="66"/>
-      <c r="R47" s="76"/>
-      <c r="S47" s="76"/>
+      <c r="R47" s="186"/>
+      <c r="S47" s="186"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="66"/>
       <c r="B48" s="66"/>
-      <c r="C48" s="69"/>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="71"/>
-      <c r="J48" s="71"/>
-      <c r="K48" s="71"/>
-      <c r="L48" s="71"/>
-      <c r="M48" s="72"/>
-      <c r="N48" s="73"/>
-      <c r="O48" s="74"/>
-      <c r="P48" s="75"/>
+      <c r="C48" s="182"/>
+      <c r="D48" s="182"/>
+      <c r="E48" s="182"/>
+      <c r="F48" s="182"/>
+      <c r="G48" s="182"/>
+      <c r="H48" s="190"/>
+      <c r="I48" s="191"/>
+      <c r="J48" s="191"/>
+      <c r="K48" s="191"/>
+      <c r="L48" s="191"/>
+      <c r="M48" s="192"/>
+      <c r="N48" s="183"/>
+      <c r="O48" s="184"/>
+      <c r="P48" s="185"/>
       <c r="Q48" s="66"/>
-      <c r="R48" s="76"/>
-      <c r="S48" s="76"/>
+      <c r="R48" s="186"/>
+      <c r="S48" s="186"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="66"/>
       <c r="B49" s="66"/>
-      <c r="C49" s="69"/>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="70"/>
-      <c r="I49" s="71"/>
-      <c r="J49" s="71"/>
-      <c r="K49" s="71"/>
-      <c r="L49" s="71"/>
-      <c r="M49" s="72"/>
-      <c r="N49" s="73"/>
-      <c r="O49" s="74"/>
-      <c r="P49" s="75"/>
+      <c r="C49" s="182"/>
+      <c r="D49" s="182"/>
+      <c r="E49" s="182"/>
+      <c r="F49" s="182"/>
+      <c r="G49" s="182"/>
+      <c r="H49" s="190"/>
+      <c r="I49" s="191"/>
+      <c r="J49" s="191"/>
+      <c r="K49" s="191"/>
+      <c r="L49" s="191"/>
+      <c r="M49" s="192"/>
+      <c r="N49" s="183"/>
+      <c r="O49" s="184"/>
+      <c r="P49" s="185"/>
       <c r="Q49" s="66"/>
-      <c r="R49" s="76"/>
-      <c r="S49" s="76"/>
+      <c r="R49" s="186"/>
+      <c r="S49" s="186"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="66"/>
       <c r="B50" s="66"/>
-      <c r="C50" s="69"/>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="69"/>
-      <c r="H50" s="70"/>
-      <c r="I50" s="71"/>
-      <c r="J50" s="71"/>
-      <c r="K50" s="71"/>
-      <c r="L50" s="71"/>
-      <c r="M50" s="72"/>
-      <c r="N50" s="73"/>
-      <c r="O50" s="74"/>
-      <c r="P50" s="75"/>
+      <c r="C50" s="182"/>
+      <c r="D50" s="182"/>
+      <c r="E50" s="182"/>
+      <c r="F50" s="182"/>
+      <c r="G50" s="182"/>
+      <c r="H50" s="190"/>
+      <c r="I50" s="191"/>
+      <c r="J50" s="191"/>
+      <c r="K50" s="191"/>
+      <c r="L50" s="191"/>
+      <c r="M50" s="192"/>
+      <c r="N50" s="183"/>
+      <c r="O50" s="184"/>
+      <c r="P50" s="185"/>
       <c r="Q50" s="66"/>
-      <c r="R50" s="76"/>
-      <c r="S50" s="76"/>
+      <c r="R50" s="186"/>
+      <c r="S50" s="186"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="66"/>
       <c r="B51" s="66"/>
-      <c r="C51" s="69"/>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="69"/>
-      <c r="H51" s="70"/>
-      <c r="I51" s="71"/>
-      <c r="J51" s="71"/>
-      <c r="K51" s="71"/>
-      <c r="L51" s="71"/>
-      <c r="M51" s="72"/>
-      <c r="N51" s="73"/>
-      <c r="O51" s="74"/>
-      <c r="P51" s="75"/>
+      <c r="C51" s="182"/>
+      <c r="D51" s="182"/>
+      <c r="E51" s="182"/>
+      <c r="F51" s="182"/>
+      <c r="G51" s="182"/>
+      <c r="H51" s="190"/>
+      <c r="I51" s="191"/>
+      <c r="J51" s="191"/>
+      <c r="K51" s="191"/>
+      <c r="L51" s="191"/>
+      <c r="M51" s="192"/>
+      <c r="N51" s="183"/>
+      <c r="O51" s="184"/>
+      <c r="P51" s="185"/>
       <c r="Q51" s="66"/>
-      <c r="R51" s="76"/>
-      <c r="S51" s="76"/>
+      <c r="R51" s="186"/>
+      <c r="S51" s="186"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="66"/>
       <c r="B52" s="66"/>
-      <c r="C52" s="69"/>
-      <c r="D52" s="69"/>
-      <c r="E52" s="69"/>
-      <c r="F52" s="69"/>
-      <c r="G52" s="69"/>
-      <c r="H52" s="70"/>
-      <c r="I52" s="71"/>
-      <c r="J52" s="71"/>
-      <c r="K52" s="71"/>
-      <c r="L52" s="71"/>
-      <c r="M52" s="72"/>
-      <c r="N52" s="73"/>
-      <c r="O52" s="74"/>
-      <c r="P52" s="75"/>
+      <c r="C52" s="182"/>
+      <c r="D52" s="182"/>
+      <c r="E52" s="182"/>
+      <c r="F52" s="182"/>
+      <c r="G52" s="182"/>
+      <c r="H52" s="190"/>
+      <c r="I52" s="191"/>
+      <c r="J52" s="191"/>
+      <c r="K52" s="191"/>
+      <c r="L52" s="191"/>
+      <c r="M52" s="192"/>
+      <c r="N52" s="183"/>
+      <c r="O52" s="184"/>
+      <c r="P52" s="185"/>
       <c r="Q52" s="66"/>
-      <c r="R52" s="76"/>
-      <c r="S52" s="76"/>
+      <c r="R52" s="186"/>
+      <c r="S52" s="186"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -13901,194 +14088,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
@@ -14152,23 +14151,23 @@
       <c r="AL1" s="40"/>
       <c r="AM1" s="40"/>
       <c r="AN1" s="40"/>
-      <c r="AO1" s="186" t="s">
+      <c r="AO1" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="AP1" s="186"/>
-      <c r="AQ1" s="186"/>
-      <c r="AR1" s="186"/>
-      <c r="AS1" s="186"/>
-      <c r="AT1" s="187">
+      <c r="AP1" s="72"/>
+      <c r="AQ1" s="72"/>
+      <c r="AR1" s="72"/>
+      <c r="AS1" s="72"/>
+      <c r="AT1" s="73">
         <v>46192</v>
       </c>
-      <c r="AU1" s="188"/>
-      <c r="AV1" s="188"/>
-      <c r="AW1" s="188"/>
-      <c r="AX1" s="188"/>
-      <c r="AY1" s="188"/>
-      <c r="AZ1" s="188"/>
-      <c r="BA1" s="188"/>
+      <c r="AU1" s="74"/>
+      <c r="AV1" s="74"/>
+      <c r="AW1" s="74"/>
+      <c r="AX1" s="74"/>
+      <c r="AY1" s="74"/>
+      <c r="AZ1" s="74"/>
+      <c r="BA1" s="74"/>
     </row>
     <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
@@ -14214,54 +14213,54 @@
       <c r="AK4" s="47"/>
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="184"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="184"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="189" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="190"/>
-      <c r="I5" s="190"/>
-      <c r="J5" s="190"/>
-      <c r="K5" s="190"/>
-      <c r="L5" s="190"/>
-      <c r="M5" s="190"/>
-      <c r="N5" s="190"/>
-      <c r="O5" s="190"/>
-      <c r="P5" s="190"/>
-      <c r="Q5" s="190"/>
-      <c r="R5" s="190"/>
-      <c r="S5" s="191"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="77"/>
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="183" t="s">
+      <c r="A6" s="69" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="184"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="185"/>
-      <c r="G6" s="192">
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="78">
         <v>1</v>
       </c>
-      <c r="H6" s="190"/>
-      <c r="I6" s="190"/>
-      <c r="J6" s="190"/>
-      <c r="K6" s="190"/>
-      <c r="L6" s="190"/>
-      <c r="M6" s="190"/>
-      <c r="N6" s="190"/>
-      <c r="O6" s="190"/>
-      <c r="P6" s="190"/>
-      <c r="Q6" s="190"/>
-      <c r="R6" s="190"/>
-      <c r="S6" s="191"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="76"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="76"/>
+      <c r="Q6" s="76"/>
+      <c r="R6" s="76"/>
+      <c r="S6" s="77"/>
     </row>
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
@@ -14270,61 +14269,61 @@
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="183" t="s">
+      <c r="A9" s="69" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="184"/>
-      <c r="C9" s="184"/>
-      <c r="D9" s="184"/>
-      <c r="E9" s="184"/>
-      <c r="F9" s="184"/>
-      <c r="G9" s="184"/>
-      <c r="H9" s="184"/>
-      <c r="I9" s="184"/>
-      <c r="J9" s="184"/>
-      <c r="K9" s="184"/>
-      <c r="L9" s="184"/>
-      <c r="M9" s="184"/>
-      <c r="N9" s="184"/>
-      <c r="O9" s="184"/>
-      <c r="P9" s="184"/>
-      <c r="Q9" s="184"/>
-      <c r="R9" s="184"/>
-      <c r="S9" s="184"/>
-      <c r="T9" s="184"/>
-      <c r="U9" s="184"/>
-      <c r="V9" s="184"/>
-      <c r="W9" s="184"/>
-      <c r="X9" s="184"/>
-      <c r="Y9" s="184"/>
-      <c r="Z9" s="184"/>
-      <c r="AA9" s="184"/>
-      <c r="AB9" s="184"/>
-      <c r="AC9" s="184"/>
-      <c r="AD9" s="184"/>
-      <c r="AE9" s="184"/>
-      <c r="AF9" s="184"/>
-      <c r="AG9" s="184"/>
-      <c r="AH9" s="184"/>
-      <c r="AI9" s="184"/>
-      <c r="AJ9" s="184"/>
-      <c r="AK9" s="184"/>
-      <c r="AL9" s="184"/>
-      <c r="AM9" s="184"/>
-      <c r="AN9" s="184"/>
-      <c r="AO9" s="184"/>
-      <c r="AP9" s="184"/>
-      <c r="AQ9" s="184"/>
-      <c r="AR9" s="184"/>
-      <c r="AS9" s="184"/>
-      <c r="AT9" s="184"/>
-      <c r="AU9" s="184"/>
-      <c r="AV9" s="184"/>
-      <c r="AW9" s="184"/>
-      <c r="AX9" s="184"/>
-      <c r="AY9" s="184"/>
-      <c r="AZ9" s="184"/>
-      <c r="BA9" s="185"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="70"/>
+      <c r="N9" s="70"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="70"/>
+      <c r="Q9" s="70"/>
+      <c r="R9" s="70"/>
+      <c r="S9" s="70"/>
+      <c r="T9" s="70"/>
+      <c r="U9" s="70"/>
+      <c r="V9" s="70"/>
+      <c r="W9" s="70"/>
+      <c r="X9" s="70"/>
+      <c r="Y9" s="70"/>
+      <c r="Z9" s="70"/>
+      <c r="AA9" s="70"/>
+      <c r="AB9" s="70"/>
+      <c r="AC9" s="70"/>
+      <c r="AD9" s="70"/>
+      <c r="AE9" s="70"/>
+      <c r="AF9" s="70"/>
+      <c r="AG9" s="70"/>
+      <c r="AH9" s="70"/>
+      <c r="AI9" s="70"/>
+      <c r="AJ9" s="70"/>
+      <c r="AK9" s="70"/>
+      <c r="AL9" s="70"/>
+      <c r="AM9" s="70"/>
+      <c r="AN9" s="70"/>
+      <c r="AO9" s="70"/>
+      <c r="AP9" s="70"/>
+      <c r="AQ9" s="70"/>
+      <c r="AR9" s="70"/>
+      <c r="AS9" s="70"/>
+      <c r="AT9" s="70"/>
+      <c r="AU9" s="70"/>
+      <c r="AV9" s="70"/>
+      <c r="AW9" s="70"/>
+      <c r="AX9" s="70"/>
+      <c r="AY9" s="70"/>
+      <c r="AZ9" s="70"/>
+      <c r="BA9" s="71"/>
     </row>
     <row r="10" spans="1:53" ht="21.95" customHeight="1">
       <c r="A10" s="49"/>
@@ -18047,61 +18046,61 @@
       <c r="BA102" s="51"/>
     </row>
     <row r="103" spans="1:53" ht="18" customHeight="1">
-      <c r="A103" s="183" t="s">
+      <c r="A103" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="B103" s="184"/>
-      <c r="C103" s="184"/>
-      <c r="D103" s="184"/>
-      <c r="E103" s="184"/>
-      <c r="F103" s="184"/>
-      <c r="G103" s="184"/>
-      <c r="H103" s="184"/>
-      <c r="I103" s="184"/>
-      <c r="J103" s="184"/>
-      <c r="K103" s="184"/>
-      <c r="L103" s="184"/>
-      <c r="M103" s="184"/>
-      <c r="N103" s="184"/>
-      <c r="O103" s="184"/>
-      <c r="P103" s="184"/>
-      <c r="Q103" s="184"/>
-      <c r="R103" s="184"/>
-      <c r="S103" s="184"/>
-      <c r="T103" s="184"/>
-      <c r="U103" s="184"/>
-      <c r="V103" s="184"/>
-      <c r="W103" s="184"/>
-      <c r="X103" s="184"/>
-      <c r="Y103" s="184"/>
-      <c r="Z103" s="184"/>
-      <c r="AA103" s="184"/>
-      <c r="AB103" s="184"/>
-      <c r="AC103" s="184"/>
-      <c r="AD103" s="184"/>
-      <c r="AE103" s="184"/>
-      <c r="AF103" s="184"/>
-      <c r="AG103" s="184"/>
-      <c r="AH103" s="184"/>
-      <c r="AI103" s="184"/>
-      <c r="AJ103" s="184"/>
-      <c r="AK103" s="184"/>
-      <c r="AL103" s="184"/>
-      <c r="AM103" s="184"/>
-      <c r="AN103" s="184"/>
-      <c r="AO103" s="184"/>
-      <c r="AP103" s="184"/>
-      <c r="AQ103" s="184"/>
-      <c r="AR103" s="184"/>
-      <c r="AS103" s="184"/>
-      <c r="AT103" s="184"/>
-      <c r="AU103" s="184"/>
-      <c r="AV103" s="184"/>
-      <c r="AW103" s="184"/>
-      <c r="AX103" s="184"/>
-      <c r="AY103" s="184"/>
-      <c r="AZ103" s="184"/>
-      <c r="BA103" s="185"/>
+      <c r="B103" s="70"/>
+      <c r="C103" s="70"/>
+      <c r="D103" s="70"/>
+      <c r="E103" s="70"/>
+      <c r="F103" s="70"/>
+      <c r="G103" s="70"/>
+      <c r="H103" s="70"/>
+      <c r="I103" s="70"/>
+      <c r="J103" s="70"/>
+      <c r="K103" s="70"/>
+      <c r="L103" s="70"/>
+      <c r="M103" s="70"/>
+      <c r="N103" s="70"/>
+      <c r="O103" s="70"/>
+      <c r="P103" s="70"/>
+      <c r="Q103" s="70"/>
+      <c r="R103" s="70"/>
+      <c r="S103" s="70"/>
+      <c r="T103" s="70"/>
+      <c r="U103" s="70"/>
+      <c r="V103" s="70"/>
+      <c r="W103" s="70"/>
+      <c r="X103" s="70"/>
+      <c r="Y103" s="70"/>
+      <c r="Z103" s="70"/>
+      <c r="AA103" s="70"/>
+      <c r="AB103" s="70"/>
+      <c r="AC103" s="70"/>
+      <c r="AD103" s="70"/>
+      <c r="AE103" s="70"/>
+      <c r="AF103" s="70"/>
+      <c r="AG103" s="70"/>
+      <c r="AH103" s="70"/>
+      <c r="AI103" s="70"/>
+      <c r="AJ103" s="70"/>
+      <c r="AK103" s="70"/>
+      <c r="AL103" s="70"/>
+      <c r="AM103" s="70"/>
+      <c r="AN103" s="70"/>
+      <c r="AO103" s="70"/>
+      <c r="AP103" s="70"/>
+      <c r="AQ103" s="70"/>
+      <c r="AR103" s="70"/>
+      <c r="AS103" s="70"/>
+      <c r="AT103" s="70"/>
+      <c r="AU103" s="70"/>
+      <c r="AV103" s="70"/>
+      <c r="AW103" s="70"/>
+      <c r="AX103" s="70"/>
+      <c r="AY103" s="70"/>
+      <c r="AZ103" s="70"/>
+      <c r="BA103" s="71"/>
     </row>
     <row r="104" spans="1:53" ht="21.95" customHeight="1">
       <c r="A104" s="52"/>
@@ -18424,61 +18423,61 @@
       <c r="BA111" s="51"/>
     </row>
     <row r="112" spans="1:53" ht="18" customHeight="1">
-      <c r="A112" s="183" t="s">
+      <c r="A112" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="B112" s="184"/>
-      <c r="C112" s="184"/>
-      <c r="D112" s="184"/>
-      <c r="E112" s="184"/>
-      <c r="F112" s="184"/>
-      <c r="G112" s="184"/>
-      <c r="H112" s="184"/>
-      <c r="I112" s="184"/>
-      <c r="J112" s="184"/>
-      <c r="K112" s="184"/>
-      <c r="L112" s="184"/>
-      <c r="M112" s="184"/>
-      <c r="N112" s="184"/>
-      <c r="O112" s="184"/>
-      <c r="P112" s="184"/>
-      <c r="Q112" s="184"/>
-      <c r="R112" s="184"/>
-      <c r="S112" s="184"/>
-      <c r="T112" s="184"/>
-      <c r="U112" s="184"/>
-      <c r="V112" s="184"/>
-      <c r="W112" s="184"/>
-      <c r="X112" s="184"/>
-      <c r="Y112" s="184"/>
-      <c r="Z112" s="184"/>
-      <c r="AA112" s="184"/>
-      <c r="AB112" s="184"/>
-      <c r="AC112" s="184"/>
-      <c r="AD112" s="184"/>
-      <c r="AE112" s="184"/>
-      <c r="AF112" s="184"/>
-      <c r="AG112" s="184"/>
-      <c r="AH112" s="184"/>
-      <c r="AI112" s="184"/>
-      <c r="AJ112" s="184"/>
-      <c r="AK112" s="184"/>
-      <c r="AL112" s="184"/>
-      <c r="AM112" s="184"/>
-      <c r="AN112" s="184"/>
-      <c r="AO112" s="184"/>
-      <c r="AP112" s="184"/>
-      <c r="AQ112" s="184"/>
-      <c r="AR112" s="184"/>
-      <c r="AS112" s="184"/>
-      <c r="AT112" s="184"/>
-      <c r="AU112" s="184"/>
-      <c r="AV112" s="184"/>
-      <c r="AW112" s="184"/>
-      <c r="AX112" s="184"/>
-      <c r="AY112" s="184"/>
-      <c r="AZ112" s="184"/>
-      <c r="BA112" s="184"/>
+      <c r="B112" s="70"/>
+      <c r="C112" s="70"/>
+      <c r="D112" s="70"/>
+      <c r="E112" s="70"/>
+      <c r="F112" s="70"/>
+      <c r="G112" s="70"/>
+      <c r="H112" s="70"/>
+      <c r="I112" s="70"/>
+      <c r="J112" s="70"/>
+      <c r="K112" s="70"/>
+      <c r="L112" s="70"/>
+      <c r="M112" s="70"/>
+      <c r="N112" s="70"/>
+      <c r="O112" s="70"/>
+      <c r="P112" s="70"/>
+      <c r="Q112" s="70"/>
+      <c r="R112" s="70"/>
+      <c r="S112" s="70"/>
+      <c r="T112" s="70"/>
+      <c r="U112" s="70"/>
+      <c r="V112" s="70"/>
+      <c r="W112" s="70"/>
+      <c r="X112" s="70"/>
+      <c r="Y112" s="70"/>
+      <c r="Z112" s="70"/>
+      <c r="AA112" s="70"/>
+      <c r="AB112" s="70"/>
+      <c r="AC112" s="70"/>
+      <c r="AD112" s="70"/>
+      <c r="AE112" s="70"/>
+      <c r="AF112" s="70"/>
+      <c r="AG112" s="70"/>
+      <c r="AH112" s="70"/>
+      <c r="AI112" s="70"/>
+      <c r="AJ112" s="70"/>
+      <c r="AK112" s="70"/>
+      <c r="AL112" s="70"/>
+      <c r="AM112" s="70"/>
+      <c r="AN112" s="70"/>
+      <c r="AO112" s="70"/>
+      <c r="AP112" s="70"/>
+      <c r="AQ112" s="70"/>
+      <c r="AR112" s="70"/>
+      <c r="AS112" s="70"/>
+      <c r="AT112" s="70"/>
+      <c r="AU112" s="70"/>
+      <c r="AV112" s="70"/>
+      <c r="AW112" s="70"/>
+      <c r="AX112" s="70"/>
+      <c r="AY112" s="70"/>
+      <c r="AZ112" s="70"/>
+      <c r="BA112" s="70"/>
     </row>
     <row r="113" spans="1:53" ht="21.95" customHeight="1">
       <c r="A113" s="52"/>
